--- a/research/traditional_assets/database/data/jamaica/jamaica_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1095975608864495</v>
+        <v>0.1093573169842333</v>
       </c>
       <c r="C2">
-        <v>9.870058856977696</v>
+        <v>9.784687931608948</v>
       </c>
       <c r="D2">
-        <v>7.580058856977696</v>
+        <v>7.592987931608949</v>
       </c>
       <c r="E2">
-        <v>-0.49</v>
+        <v>-0.3917</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0983</v>
       </c>
       <c r="G2">
         <v>2.29</v>
@@ -1451,28 +1451,28 @@
         <v>1.123</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004944489999999999</v>
       </c>
       <c r="N2">
-        <v>1.123</v>
+        <v>1.11805551</v>
       </c>
       <c r="O2">
-        <v>0.28075</v>
+        <v>0.2795138775</v>
       </c>
       <c r="P2">
-        <v>0.8422499999999999</v>
+        <v>0.8385416325</v>
       </c>
       <c r="Q2">
-        <v>1.17925</v>
+        <v>1.1755416325</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1095975608864495</v>
+        <v>0.1100808757416498</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6216451971634287</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>227.1215029254787</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1093573169842333</v>
+        <v>0.1091170730820172</v>
       </c>
       <c r="C3">
-        <v>9.784687931608948</v>
+        <v>9.699361187052645</v>
       </c>
       <c r="D3">
-        <v>7.592987931608949</v>
+        <v>7.605961187052644</v>
       </c>
       <c r="E3">
-        <v>-0.3917</v>
+        <v>-0.2934</v>
       </c>
       <c r="F3">
-        <v>0.0983</v>
+        <v>0.1966</v>
       </c>
       <c r="G3">
         <v>2.29</v>
@@ -1533,28 +1533,28 @@
         <v>1.123</v>
       </c>
       <c r="M3">
-        <v>0.004944489999999999</v>
+        <v>0.009888979999999999</v>
       </c>
       <c r="N3">
-        <v>1.11805551</v>
+        <v>1.11311102</v>
       </c>
       <c r="O3">
-        <v>0.2795138775</v>
+        <v>0.278277755</v>
       </c>
       <c r="P3">
-        <v>0.8385416325</v>
+        <v>0.8348332650000001</v>
       </c>
       <c r="Q3">
-        <v>1.1755416325</v>
+        <v>1.171833265</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1100808757416498</v>
+        <v>0.1105740541653237</v>
       </c>
       <c r="T3">
-        <v>0.6216451971634287</v>
+        <v>0.6264146094479418</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>227.1215029254787</v>
+        <v>113.5607514627394</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1091170730820172</v>
+        <v>0.1088768291798011</v>
       </c>
       <c r="C4">
-        <v>9.699361187052645</v>
+        <v>9.61407885015622</v>
       </c>
       <c r="D4">
-        <v>7.605961187052644</v>
+        <v>7.618978850156219</v>
       </c>
       <c r="E4">
-        <v>-0.2934</v>
+        <v>-0.1951</v>
       </c>
       <c r="F4">
-        <v>0.1966</v>
+        <v>0.2949</v>
       </c>
       <c r="G4">
         <v>2.29</v>
@@ -1615,28 +1615,28 @@
         <v>1.123</v>
       </c>
       <c r="M4">
-        <v>0.009888979999999999</v>
+        <v>0.01483347</v>
       </c>
       <c r="N4">
-        <v>1.11311102</v>
+        <v>1.10816653</v>
       </c>
       <c r="O4">
-        <v>0.278277755</v>
+        <v>0.2770416325</v>
       </c>
       <c r="P4">
-        <v>0.8348332650000001</v>
+        <v>0.8311248975000001</v>
       </c>
       <c r="Q4">
-        <v>1.171833265</v>
+        <v>1.1681248975</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1105740541653237</v>
+        <v>0.1110774012162898</v>
       </c>
       <c r="T4">
-        <v>0.6264146094479418</v>
+        <v>0.6312823601300735</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.5607514627394</v>
+        <v>75.70716764182623</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1088768291798011</v>
+        <v>0.1086365852775849</v>
       </c>
       <c r="C5">
-        <v>9.61407885015622</v>
+        <v>9.528841149322776</v>
       </c>
       <c r="D5">
-        <v>7.618978850156219</v>
+        <v>7.632041149322776</v>
       </c>
       <c r="E5">
-        <v>-0.1951</v>
+        <v>-0.0968</v>
       </c>
       <c r="F5">
-        <v>0.2949</v>
+        <v>0.3932</v>
       </c>
       <c r="G5">
         <v>2.29</v>
@@ -1697,28 +1697,28 @@
         <v>1.123</v>
       </c>
       <c r="M5">
-        <v>0.01483347</v>
+        <v>0.01977796</v>
       </c>
       <c r="N5">
-        <v>1.10816653</v>
+        <v>1.10322204</v>
       </c>
       <c r="O5">
-        <v>0.2770416325</v>
+        <v>0.27580551</v>
       </c>
       <c r="P5">
-        <v>0.8311248975000001</v>
+        <v>0.8274165299999999</v>
       </c>
       <c r="Q5">
-        <v>1.1681248975</v>
+        <v>1.16441653</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1110774012162898</v>
+        <v>0.111591234664151</v>
       </c>
       <c r="T5">
-        <v>0.6312823601300735</v>
+        <v>0.6362515222847499</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.70716764182623</v>
+        <v>56.78037573136967</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1086365852775849</v>
+        <v>0.1083963413753688</v>
       </c>
       <c r="C6">
-        <v>9.528841149322776</v>
+        <v>9.443648314524442</v>
       </c>
       <c r="D6">
-        <v>7.632041149322776</v>
+        <v>7.645148314524442</v>
       </c>
       <c r="E6">
-        <v>-0.0968</v>
+        <v>0.001500000000000057</v>
       </c>
       <c r="F6">
-        <v>0.3932</v>
+        <v>0.4915</v>
       </c>
       <c r="G6">
         <v>2.29</v>
@@ -1779,28 +1779,28 @@
         <v>1.123</v>
       </c>
       <c r="M6">
-        <v>0.01977796</v>
+        <v>0.02472245</v>
       </c>
       <c r="N6">
-        <v>1.10322204</v>
+        <v>1.09827755</v>
       </c>
       <c r="O6">
-        <v>0.27580551</v>
+        <v>0.2745693875</v>
       </c>
       <c r="P6">
-        <v>0.8274165299999999</v>
+        <v>0.8237081625</v>
       </c>
       <c r="Q6">
-        <v>1.16441653</v>
+        <v>1.1607081625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.111591234664151</v>
+        <v>0.112115885658283</v>
       </c>
       <c r="T6">
-        <v>0.6362515222847499</v>
+        <v>0.6413252983795246</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.78037573136967</v>
+        <v>45.42430058509573</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1083963413753688</v>
+        <v>0.1081560974731527</v>
       </c>
       <c r="C7">
-        <v>9.443648314524442</v>
+        <v>9.358500577315873</v>
       </c>
       <c r="D7">
-        <v>7.645148314524442</v>
+        <v>7.658300577315873</v>
       </c>
       <c r="E7">
-        <v>0.001500000000000057</v>
+        <v>0.09980000000000011</v>
       </c>
       <c r="F7">
-        <v>0.4915</v>
+        <v>0.5898000000000001</v>
       </c>
       <c r="G7">
         <v>2.29</v>
@@ -1861,28 +1861,28 @@
         <v>1.123</v>
       </c>
       <c r="M7">
-        <v>0.02472245</v>
+        <v>0.02966694</v>
       </c>
       <c r="N7">
-        <v>1.09827755</v>
+        <v>1.09333306</v>
       </c>
       <c r="O7">
-        <v>0.2745693875</v>
+        <v>0.273333265</v>
       </c>
       <c r="P7">
-        <v>0.8237081625</v>
+        <v>0.819999795</v>
       </c>
       <c r="Q7">
-        <v>1.1607081625</v>
+        <v>1.156999795</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.112115885658283</v>
+        <v>0.1126516994395242</v>
       </c>
       <c r="T7">
-        <v>0.6413252983795246</v>
+        <v>0.6465070271571668</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.42430058509573</v>
+        <v>37.85358382091311</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1081560974731527</v>
+        <v>0.1079158535709366</v>
       </c>
       <c r="C8">
-        <v>9.358500577315873</v>
+        <v>9.273398170847878</v>
       </c>
       <c r="D8">
-        <v>7.658300577315873</v>
+        <v>7.671498170847878</v>
       </c>
       <c r="E8">
-        <v>0.0998</v>
+        <v>0.1980999999999999</v>
       </c>
       <c r="F8">
-        <v>0.5898</v>
+        <v>0.6880999999999999</v>
       </c>
       <c r="G8">
         <v>2.29</v>
@@ -1943,28 +1943,28 @@
         <v>1.123</v>
       </c>
       <c r="M8">
-        <v>0.02966694</v>
+        <v>0.03461142999999999</v>
       </c>
       <c r="N8">
-        <v>1.09333306</v>
+        <v>1.08838857</v>
       </c>
       <c r="O8">
-        <v>0.273333265</v>
+        <v>0.2720971425</v>
       </c>
       <c r="P8">
-        <v>0.819999795</v>
+        <v>0.8162914274999999</v>
       </c>
       <c r="Q8">
-        <v>1.156999795</v>
+        <v>1.1532914275</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1126516994395242</v>
+        <v>0.1131990360977813</v>
       </c>
       <c r="T8">
-        <v>0.6465070271571668</v>
+        <v>0.6518001909622853</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.85358382091311</v>
+        <v>32.4459289893541</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1079158535709366</v>
+        <v>0.1076756096687205</v>
       </c>
       <c r="C9">
-        <v>9.273398170847878</v>
+        <v>9.188341329881196</v>
       </c>
       <c r="D9">
-        <v>7.671498170847878</v>
+        <v>7.684741329881196</v>
       </c>
       <c r="E9">
-        <v>0.1981000000000001</v>
+        <v>0.2964</v>
       </c>
       <c r="F9">
-        <v>0.6881</v>
+        <v>0.7864</v>
       </c>
       <c r="G9">
         <v>2.29</v>
@@ -2025,28 +2025,28 @@
         <v>1.123</v>
       </c>
       <c r="M9">
-        <v>0.03461143</v>
+        <v>0.03955591999999999</v>
       </c>
       <c r="N9">
-        <v>1.08838857</v>
+        <v>1.08344408</v>
       </c>
       <c r="O9">
-        <v>0.2720971425</v>
+        <v>0.27086102</v>
       </c>
       <c r="P9">
-        <v>0.8162914274999999</v>
+        <v>0.81258306</v>
       </c>
       <c r="Q9">
-        <v>1.1532914275</v>
+        <v>1.14958306</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1131990360977813</v>
+        <v>0.113758271379044</v>
       </c>
       <c r="T9">
-        <v>0.6518001909622853</v>
+        <v>0.6572084235457759</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.4459289893541</v>
+        <v>28.39018786568484</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1076756096687205</v>
+        <v>0.1074353657665043</v>
       </c>
       <c r="C10">
-        <v>9.188341329881196</v>
+        <v>9.103330290800431</v>
       </c>
       <c r="D10">
-        <v>7.684741329881196</v>
+        <v>7.698030290800432</v>
       </c>
       <c r="E10">
-        <v>0.2964</v>
+        <v>0.3946999999999999</v>
       </c>
       <c r="F10">
-        <v>0.7864</v>
+        <v>0.8846999999999999</v>
       </c>
       <c r="G10">
         <v>2.29</v>
@@ -2107,28 +2107,28 @@
         <v>1.123</v>
       </c>
       <c r="M10">
-        <v>0.03955591999999999</v>
+        <v>0.04450041</v>
       </c>
       <c r="N10">
-        <v>1.08344408</v>
+        <v>1.07849959</v>
       </c>
       <c r="O10">
-        <v>0.27086102</v>
+        <v>0.2696248975</v>
       </c>
       <c r="P10">
-        <v>0.81258306</v>
+        <v>0.8088746925000001</v>
       </c>
       <c r="Q10">
-        <v>1.14958306</v>
+        <v>1.1458746925</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.113758271379044</v>
+        <v>0.1143297975456092</v>
       </c>
       <c r="T10">
-        <v>0.6572084235457759</v>
+        <v>0.6627355183838486</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.39018786568484</v>
+        <v>25.23572254727541</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1074353657665043</v>
+        <v>0.1071951218642882</v>
       </c>
       <c r="C11">
-        <v>9.103330290800431</v>
+        <v>9.018365291628101</v>
       </c>
       <c r="D11">
-        <v>7.698030290800432</v>
+        <v>7.711365291628102</v>
       </c>
       <c r="E11">
-        <v>0.3946999999999999</v>
+        <v>0.4929999999999999</v>
       </c>
       <c r="F11">
-        <v>0.8846999999999999</v>
+        <v>0.9829999999999999</v>
       </c>
       <c r="G11">
         <v>2.29</v>
@@ -2189,28 +2189,28 @@
         <v>1.123</v>
       </c>
       <c r="M11">
-        <v>0.04450041</v>
+        <v>0.04944489999999999</v>
       </c>
       <c r="N11">
-        <v>1.07849959</v>
+        <v>1.0735551</v>
       </c>
       <c r="O11">
-        <v>0.2696248975</v>
+        <v>0.268388775</v>
       </c>
       <c r="P11">
-        <v>0.8088746925000001</v>
+        <v>0.8051663250000001</v>
       </c>
       <c r="Q11">
-        <v>1.1458746925</v>
+        <v>1.142166325</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1143297975456092</v>
+        <v>0.1149140242936535</v>
       </c>
       <c r="T11">
-        <v>0.6627355183838486</v>
+        <v>0.6683854375516564</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.23572254727541</v>
+        <v>22.71215029254787</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1071951218642882</v>
+        <v>0.1069548779620721</v>
       </c>
       <c r="C12">
-        <v>9.018365291628101</v>
+        <v>8.933446572038855</v>
       </c>
       <c r="D12">
-        <v>7.711365291628102</v>
+        <v>7.724746572038857</v>
       </c>
       <c r="E12">
-        <v>0.4930000000000001</v>
+        <v>0.5912999999999999</v>
       </c>
       <c r="F12">
-        <v>0.9830000000000001</v>
+        <v>1.0813</v>
       </c>
       <c r="G12">
         <v>2.29</v>
@@ -2271,28 +2271,28 @@
         <v>1.123</v>
       </c>
       <c r="M12">
-        <v>0.0494449</v>
+        <v>0.05438939</v>
       </c>
       <c r="N12">
-        <v>1.0735551</v>
+        <v>1.06861061</v>
       </c>
       <c r="O12">
-        <v>0.268388775</v>
+        <v>0.2671526525</v>
       </c>
       <c r="P12">
-        <v>0.8051663250000001</v>
+        <v>0.8014579574999999</v>
       </c>
       <c r="Q12">
-        <v>1.142166325</v>
+        <v>1.1384579575</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1149140242936535</v>
+        <v>0.1155113797326653</v>
       </c>
       <c r="T12">
-        <v>0.6683854375516564</v>
+        <v>0.6741623211951453</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.71215029254787</v>
+        <v>20.6474093568617</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1069548779620721</v>
+        <v>0.106714634059856</v>
       </c>
       <c r="C13">
-        <v>8.933446572038855</v>
+        <v>8.848574373373832</v>
       </c>
       <c r="D13">
-        <v>7.724746572038857</v>
+        <v>7.738174373373834</v>
       </c>
       <c r="E13">
-        <v>0.5912999999999999</v>
+        <v>0.6896</v>
       </c>
       <c r="F13">
-        <v>1.0813</v>
+        <v>1.1796</v>
       </c>
       <c r="G13">
         <v>2.29</v>
@@ -2353,28 +2353,28 @@
         <v>1.123</v>
       </c>
       <c r="M13">
-        <v>0.05438939</v>
+        <v>0.05933388</v>
       </c>
       <c r="N13">
-        <v>1.06861061</v>
+        <v>1.06366612</v>
       </c>
       <c r="O13">
-        <v>0.2671526525</v>
+        <v>0.26591653</v>
       </c>
       <c r="P13">
-        <v>0.8014579574999999</v>
+        <v>0.79774959</v>
       </c>
       <c r="Q13">
-        <v>1.1384579575</v>
+        <v>1.13474959</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1155113797326653</v>
+        <v>0.1161223114316545</v>
       </c>
       <c r="T13">
-        <v>0.6741623211951453</v>
+        <v>0.6800704976487133</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.6474093568617</v>
+        <v>18.92679191045655</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.106714634059856</v>
+        <v>0.1064743901576398</v>
       </c>
       <c r="C14">
-        <v>8.848574373373832</v>
+        <v>8.763748938655173</v>
       </c>
       <c r="D14">
-        <v>7.738174373373834</v>
+        <v>7.751648938655173</v>
       </c>
       <c r="E14">
-        <v>0.6896</v>
+        <v>0.7879</v>
       </c>
       <c r="F14">
-        <v>1.1796</v>
+        <v>1.2779</v>
       </c>
       <c r="G14">
         <v>2.29</v>
@@ -2435,28 +2435,28 @@
         <v>1.123</v>
       </c>
       <c r="M14">
-        <v>0.05933388</v>
+        <v>0.06427837</v>
       </c>
       <c r="N14">
-        <v>1.06366612</v>
+        <v>1.05872163</v>
       </c>
       <c r="O14">
-        <v>0.26591653</v>
+        <v>0.2646804075</v>
       </c>
       <c r="P14">
-        <v>0.79774959</v>
+        <v>0.7940412225</v>
       </c>
       <c r="Q14">
-        <v>1.13474959</v>
+        <v>1.1310412225</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1161223114316545</v>
+        <v>0.1167472875375171</v>
       </c>
       <c r="T14">
-        <v>0.6800704976487133</v>
+        <v>0.6861144942506393</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.92679191045655</v>
+        <v>17.47088484042143</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1064743901576398</v>
+        <v>0.1062341462554237</v>
       </c>
       <c r="C15">
-        <v>8.763748938655173</v>
+        <v>8.678970512600678</v>
       </c>
       <c r="D15">
-        <v>7.751648938655173</v>
+        <v>7.765170512600679</v>
       </c>
       <c r="E15">
-        <v>0.7879</v>
+        <v>0.8862000000000001</v>
       </c>
       <c r="F15">
-        <v>1.2779</v>
+        <v>1.3762</v>
       </c>
       <c r="G15">
         <v>2.29</v>
@@ -2517,28 +2517,28 @@
         <v>1.123</v>
       </c>
       <c r="M15">
-        <v>0.06427837</v>
+        <v>0.06922286</v>
       </c>
       <c r="N15">
-        <v>1.05872163</v>
+        <v>1.05377714</v>
       </c>
       <c r="O15">
-        <v>0.2646804075</v>
+        <v>0.263444285</v>
       </c>
       <c r="P15">
-        <v>0.7940412225</v>
+        <v>0.7903328549999999</v>
       </c>
       <c r="Q15">
-        <v>1.1310412225</v>
+        <v>1.127332855</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1167472875375171</v>
+        <v>0.1173867979714229</v>
       </c>
       <c r="T15">
-        <v>0.6861144942506393</v>
+        <v>0.6922990489130753</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.47088484042143</v>
+        <v>16.22296449467705</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1062341462554237</v>
+        <v>0.1059939023532076</v>
       </c>
       <c r="C16">
-        <v>8.678970512600678</v>
+        <v>8.594239341638621</v>
       </c>
       <c r="D16">
-        <v>7.765170512600679</v>
+        <v>7.778739341638623</v>
       </c>
       <c r="E16">
-        <v>0.8862000000000001</v>
+        <v>0.9845000000000002</v>
       </c>
       <c r="F16">
-        <v>1.3762</v>
+        <v>1.4745</v>
       </c>
       <c r="G16">
         <v>2.29</v>
@@ -2599,28 +2599,28 @@
         <v>1.123</v>
       </c>
       <c r="M16">
-        <v>0.06922286</v>
+        <v>0.07416735000000001</v>
       </c>
       <c r="N16">
-        <v>1.05377714</v>
+        <v>1.04883265</v>
       </c>
       <c r="O16">
-        <v>0.263444285</v>
+        <v>0.2622081625</v>
       </c>
       <c r="P16">
-        <v>0.7903328549999999</v>
+        <v>0.7866244875</v>
       </c>
       <c r="Q16">
-        <v>1.127332855</v>
+        <v>1.1236244875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1173867979714229</v>
+        <v>0.118041355709656</v>
       </c>
       <c r="T16">
-        <v>0.6922990489130753</v>
+        <v>0.6986291225087449</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.22296449467705</v>
+        <v>15.14143352836524</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1059939023532076</v>
+        <v>0.1057536584509915</v>
       </c>
       <c r="C17">
-        <v>8.594239341638623</v>
+        <v>8.509555673922726</v>
       </c>
       <c r="D17">
-        <v>7.778739341638623</v>
+        <v>7.792355673922728</v>
       </c>
       <c r="E17">
-        <v>0.9844999999999999</v>
+        <v>1.0828</v>
       </c>
       <c r="F17">
-        <v>1.4745</v>
+        <v>1.5728</v>
       </c>
       <c r="G17">
         <v>2.29</v>
@@ -2681,28 +2681,28 @@
         <v>1.123</v>
       </c>
       <c r="M17">
-        <v>0.07416734999999999</v>
+        <v>0.07911183999999999</v>
       </c>
       <c r="N17">
-        <v>1.04883265</v>
+        <v>1.04388816</v>
       </c>
       <c r="O17">
-        <v>0.2622081625</v>
+        <v>0.26097204</v>
       </c>
       <c r="P17">
-        <v>0.7866244875</v>
+        <v>0.7829161200000001</v>
       </c>
       <c r="Q17">
-        <v>1.1236244875</v>
+        <v>1.11991612</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.118041355709656</v>
+        <v>0.1187114981559422</v>
       </c>
       <c r="T17">
-        <v>0.6986291225087449</v>
+        <v>0.7051099121424067</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.14143352836525</v>
+        <v>14.19509393284242</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1057536584509915</v>
+        <v>0.1055134145487753</v>
       </c>
       <c r="C18">
-        <v>8.509555673922726</v>
+        <v>8.424919759347294</v>
       </c>
       <c r="D18">
-        <v>7.792355673922728</v>
+        <v>7.806019759347293</v>
       </c>
       <c r="E18">
-        <v>1.0828</v>
+        <v>1.1811</v>
       </c>
       <c r="F18">
-        <v>1.5728</v>
+        <v>1.6711</v>
       </c>
       <c r="G18">
         <v>2.29</v>
@@ -2763,28 +2763,28 @@
         <v>1.123</v>
       </c>
       <c r="M18">
-        <v>0.07911183999999999</v>
+        <v>0.08405633</v>
       </c>
       <c r="N18">
-        <v>1.04388816</v>
+        <v>1.03894367</v>
       </c>
       <c r="O18">
-        <v>0.26097204</v>
+        <v>0.2597359175</v>
       </c>
       <c r="P18">
-        <v>0.7829161200000001</v>
+        <v>0.7792077525000001</v>
       </c>
       <c r="Q18">
-        <v>1.11991612</v>
+        <v>1.1162077525</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1187114981559422</v>
+        <v>0.1193977886129823</v>
       </c>
       <c r="T18">
-        <v>0.7051099121424067</v>
+        <v>0.7117468653816991</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.19509393284242</v>
+        <v>13.3600884073811</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1055134145487753</v>
+        <v>0.1054756706465592</v>
       </c>
       <c r="C19">
-        <v>8.424919759347294</v>
+        <v>8.328770834248299</v>
       </c>
       <c r="D19">
-        <v>7.806019759347293</v>
+        <v>7.8081708342483</v>
       </c>
       <c r="E19">
-        <v>1.1811</v>
+        <v>1.2794</v>
       </c>
       <c r="F19">
-        <v>1.6711</v>
+        <v>1.7694</v>
       </c>
       <c r="G19">
         <v>2.29</v>
@@ -2845,45 +2845,45 @@
         <v>1.123</v>
       </c>
       <c r="M19">
-        <v>0.08405633</v>
+        <v>0.09165492000000001</v>
       </c>
       <c r="N19">
-        <v>1.03894367</v>
+        <v>1.03134508</v>
       </c>
       <c r="O19">
-        <v>0.2597359175</v>
+        <v>0.25783627</v>
       </c>
       <c r="P19">
-        <v>0.7792077525000001</v>
+        <v>0.7735088099999999</v>
       </c>
       <c r="Q19">
-        <v>1.1162077525</v>
+        <v>1.11050881</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1193977886129823</v>
+        <v>0.1201008178616576</v>
       </c>
       <c r="T19">
-        <v>0.7117468653816991</v>
+        <v>0.7185456955292666</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.3600884073811</v>
+        <v>12.25247919042425</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1054756706465592</v>
+        <v>0.1052466767443431</v>
       </c>
       <c r="C20">
-        <v>8.328770834248301</v>
+        <v>8.243546957489393</v>
       </c>
       <c r="D20">
-        <v>7.8081708342483</v>
+        <v>7.821246957489392</v>
       </c>
       <c r="E20">
-        <v>1.2794</v>
+        <v>1.3777</v>
       </c>
       <c r="F20">
-        <v>1.7694</v>
+        <v>1.8677</v>
       </c>
       <c r="G20">
         <v>2.29</v>
@@ -2927,28 +2927,28 @@
         <v>1.123</v>
       </c>
       <c r="M20">
-        <v>0.09165491999999999</v>
+        <v>0.09674686</v>
       </c>
       <c r="N20">
-        <v>1.03134508</v>
+        <v>1.02625314</v>
       </c>
       <c r="O20">
-        <v>0.25783627</v>
+        <v>0.256563285</v>
       </c>
       <c r="P20">
-        <v>0.7735088099999999</v>
+        <v>0.769689855</v>
       </c>
       <c r="Q20">
-        <v>1.11050881</v>
+        <v>1.106689855</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1201008178616576</v>
+        <v>0.1208212058572137</v>
       </c>
       <c r="T20">
-        <v>0.7185456955292666</v>
+        <v>0.7255123980261571</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.25247919042426</v>
+        <v>11.60761186461245</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1052466767443431</v>
+        <v>0.105017682842127</v>
       </c>
       <c r="C21">
-        <v>8.243546957489393</v>
+        <v>8.15836695062697</v>
       </c>
       <c r="D21">
-        <v>7.821246957489392</v>
+        <v>7.834366950626969</v>
       </c>
       <c r="E21">
-        <v>1.3777</v>
+        <v>1.476</v>
       </c>
       <c r="F21">
-        <v>1.8677</v>
+        <v>1.966</v>
       </c>
       <c r="G21">
         <v>2.29</v>
@@ -3009,28 +3009,28 @@
         <v>1.123</v>
       </c>
       <c r="M21">
-        <v>0.09674686</v>
+        <v>0.1018388</v>
       </c>
       <c r="N21">
-        <v>1.02625314</v>
+        <v>1.0211612</v>
       </c>
       <c r="O21">
-        <v>0.256563285</v>
+        <v>0.2552903</v>
       </c>
       <c r="P21">
-        <v>0.769689855</v>
+        <v>0.7658708999999999</v>
       </c>
       <c r="Q21">
-        <v>1.106689855</v>
+        <v>1.1028709</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1208212058572137</v>
+        <v>0.1215596035526587</v>
       </c>
       <c r="T21">
-        <v>0.7255123980261571</v>
+        <v>0.7326532680854695</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.60761186461245</v>
+        <v>11.02723127138183</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.105017682842127</v>
+        <v>0.1047886889399108</v>
       </c>
       <c r="C22">
-        <v>8.15836695062697</v>
+        <v>8.073231034804746</v>
       </c>
       <c r="D22">
-        <v>7.834366950626969</v>
+        <v>7.847531034804744</v>
       </c>
       <c r="E22">
-        <v>1.476</v>
+        <v>1.5743</v>
       </c>
       <c r="F22">
-        <v>1.966</v>
+        <v>2.0643</v>
       </c>
       <c r="G22">
         <v>2.29</v>
@@ -3091,28 +3091,28 @@
         <v>1.123</v>
       </c>
       <c r="M22">
-        <v>0.1018388</v>
+        <v>0.10693074</v>
       </c>
       <c r="N22">
-        <v>1.0211612</v>
+        <v>1.01606926</v>
       </c>
       <c r="O22">
-        <v>0.2552903</v>
+        <v>0.254017315</v>
       </c>
       <c r="P22">
-        <v>0.7658708999999999</v>
+        <v>0.7620519450000001</v>
       </c>
       <c r="Q22">
-        <v>1.1028709</v>
+        <v>1.099051945</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1215596035526587</v>
+        <v>0.1223166948606466</v>
       </c>
       <c r="T22">
-        <v>0.7326532680854695</v>
+        <v>0.739974919665271</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.02723127138183</v>
+        <v>10.50212502036365</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1047886889399108</v>
+        <v>0.1045596950376947</v>
       </c>
       <c r="C23">
-        <v>8.073231034804746</v>
+        <v>7.988139432655286</v>
       </c>
       <c r="D23">
-        <v>7.847531034804744</v>
+        <v>7.860739432655286</v>
       </c>
       <c r="E23">
-        <v>1.5743</v>
+        <v>1.6726</v>
       </c>
       <c r="F23">
-        <v>2.0643</v>
+        <v>2.1626</v>
       </c>
       <c r="G23">
         <v>2.29</v>
@@ -3173,28 +3173,28 @@
         <v>1.123</v>
       </c>
       <c r="M23">
-        <v>0.10693074</v>
+        <v>0.11202268</v>
       </c>
       <c r="N23">
-        <v>1.01606926</v>
+        <v>1.01097732</v>
       </c>
       <c r="O23">
-        <v>0.254017315</v>
+        <v>0.25274433</v>
       </c>
       <c r="P23">
-        <v>0.7620519450000001</v>
+        <v>0.75823299</v>
       </c>
       <c r="Q23">
-        <v>1.099051945</v>
+        <v>1.09523299</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1223166948606466</v>
+        <v>0.1230931987662753</v>
       </c>
       <c r="T23">
-        <v>0.739974919665271</v>
+        <v>0.7474843059009648</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.50212502036365</v>
+        <v>10.02475570125621</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1045596950376947</v>
+        <v>0.1046239511354786</v>
       </c>
       <c r="C24">
-        <v>7.988139432655286</v>
+        <v>7.886128647022845</v>
       </c>
       <c r="D24">
-        <v>7.860739432655286</v>
+        <v>7.857028647022845</v>
       </c>
       <c r="E24">
-        <v>1.6726</v>
+        <v>1.7709</v>
       </c>
       <c r="F24">
-        <v>2.1626</v>
+        <v>2.2609</v>
       </c>
       <c r="G24">
         <v>2.29</v>
@@ -3255,45 +3255,45 @@
         <v>1.123</v>
       </c>
       <c r="M24">
-        <v>0.11202268</v>
+        <v>0.12095815</v>
       </c>
       <c r="N24">
-        <v>1.01097732</v>
+        <v>1.00204185</v>
       </c>
       <c r="O24">
-        <v>0.25274433</v>
+        <v>0.2505104625</v>
       </c>
       <c r="P24">
-        <v>0.75823299</v>
+        <v>0.7515313874999999</v>
       </c>
       <c r="Q24">
-        <v>1.09523299</v>
+        <v>1.0885313875</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1230931987662753</v>
+        <v>0.1238898716045177</v>
       </c>
       <c r="T24">
-        <v>0.7474843059009648</v>
+        <v>0.7551887411297936</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.02475570125621</v>
+        <v>9.284202842057356</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1046239511354786</v>
+        <v>0.1044077072332625</v>
       </c>
       <c r="C25">
-        <v>7.886128647022845</v>
+        <v>7.800330685209699</v>
       </c>
       <c r="D25">
-        <v>7.857028647022845</v>
+        <v>7.8695306852097</v>
       </c>
       <c r="E25">
-        <v>1.7709</v>
+        <v>1.8692</v>
       </c>
       <c r="F25">
-        <v>2.2609</v>
+        <v>2.3592</v>
       </c>
       <c r="G25">
         <v>2.29</v>
@@ -3337,28 +3337,28 @@
         <v>1.123</v>
       </c>
       <c r="M25">
-        <v>0.12095815</v>
+        <v>0.1262172</v>
       </c>
       <c r="N25">
-        <v>1.00204185</v>
+        <v>0.9967828</v>
       </c>
       <c r="O25">
-        <v>0.2505104625</v>
+        <v>0.2491957</v>
       </c>
       <c r="P25">
-        <v>0.7515313874999999</v>
+        <v>0.7475870999999999</v>
       </c>
       <c r="Q25">
-        <v>1.0885313875</v>
+        <v>1.0845871</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1238898716045177</v>
+        <v>0.1247075095174506</v>
       </c>
       <c r="T25">
-        <v>0.7551887411297936</v>
+        <v>0.7630959246541179</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.284202842057356</v>
+        <v>8.897361056971631</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1044077072332625</v>
+        <v>0.1041914633310464</v>
       </c>
       <c r="C26">
-        <v>7.800330685209699</v>
+        <v>7.714572573081977</v>
       </c>
       <c r="D26">
-        <v>7.8695306852097</v>
+        <v>7.882072573081976</v>
       </c>
       <c r="E26">
-        <v>1.8692</v>
+        <v>1.9675</v>
       </c>
       <c r="F26">
-        <v>2.3592</v>
+        <v>2.4575</v>
       </c>
       <c r="G26">
         <v>2.29</v>
@@ -3419,28 +3419,28 @@
         <v>1.123</v>
       </c>
       <c r="M26">
-        <v>0.1262172</v>
+        <v>0.13147625</v>
       </c>
       <c r="N26">
-        <v>0.9967828</v>
+        <v>0.99152375</v>
       </c>
       <c r="O26">
-        <v>0.2491957</v>
+        <v>0.2478809375</v>
       </c>
       <c r="P26">
-        <v>0.7475870999999999</v>
+        <v>0.7436428125000001</v>
       </c>
       <c r="Q26">
-        <v>1.0845871</v>
+        <v>1.0806428125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1247075095174506</v>
+        <v>0.1255469511080618</v>
       </c>
       <c r="T26">
-        <v>0.7630959246541179</v>
+        <v>0.7712139664057573</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.897361056971633</v>
+        <v>8.541466614692769</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1041914633310464</v>
+        <v>0.1039752194288302</v>
       </c>
       <c r="C27">
-        <v>7.714572573081977</v>
+        <v>7.628854501472437</v>
       </c>
       <c r="D27">
-        <v>7.882072573081976</v>
+        <v>7.894654501472436</v>
       </c>
       <c r="E27">
-        <v>1.9675</v>
+        <v>2.0658</v>
       </c>
       <c r="F27">
-        <v>2.4575</v>
+        <v>2.5558</v>
       </c>
       <c r="G27">
         <v>2.29</v>
@@ -3501,28 +3501,28 @@
         <v>1.123</v>
       </c>
       <c r="M27">
-        <v>0.13147625</v>
+        <v>0.1367353</v>
       </c>
       <c r="N27">
-        <v>0.99152375</v>
+        <v>0.9862647</v>
       </c>
       <c r="O27">
-        <v>0.2478809375</v>
+        <v>0.246566175</v>
       </c>
       <c r="P27">
-        <v>0.7436428125000001</v>
+        <v>0.739698525</v>
       </c>
       <c r="Q27">
-        <v>1.0806428125</v>
+        <v>1.076698525</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1255469511080618</v>
+        <v>0.1264090803092301</v>
       </c>
       <c r="T27">
-        <v>0.7712139664057573</v>
+        <v>0.7795514146912251</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.541466614692769</v>
+        <v>8.212948667973816</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1039752194288302</v>
+        <v>0.1037589755266141</v>
       </c>
       <c r="C28">
-        <v>7.628854501472437</v>
+        <v>7.543176662434272</v>
       </c>
       <c r="D28">
-        <v>7.894654501472436</v>
+        <v>7.907276662434271</v>
       </c>
       <c r="E28">
-        <v>2.0658</v>
+        <v>2.1641</v>
       </c>
       <c r="F28">
-        <v>2.5558</v>
+        <v>2.6541</v>
       </c>
       <c r="G28">
         <v>2.29</v>
@@ -3583,28 +3583,28 @@
         <v>1.123</v>
       </c>
       <c r="M28">
-        <v>0.1367353</v>
+        <v>0.14199435</v>
       </c>
       <c r="N28">
-        <v>0.9862647</v>
+        <v>0.98100565</v>
       </c>
       <c r="O28">
-        <v>0.246566175</v>
+        <v>0.2452514125</v>
       </c>
       <c r="P28">
-        <v>0.739698525</v>
+        <v>0.7357542374999999</v>
       </c>
       <c r="Q28">
-        <v>1.076698525</v>
+        <v>1.0727542375</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1264090803092301</v>
+        <v>0.1272948294885125</v>
       </c>
       <c r="T28">
-        <v>0.7795514146912251</v>
+        <v>0.7881172862173905</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.212948667973816</v>
+        <v>7.908765383974785</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1037589755266141</v>
+        <v>0.103542731624398</v>
       </c>
       <c r="C29">
-        <v>7.543176662434272</v>
+        <v>7.457539249250877</v>
       </c>
       <c r="D29">
-        <v>7.907276662434271</v>
+        <v>7.919939249250875</v>
       </c>
       <c r="E29">
-        <v>2.1641</v>
+        <v>2.2624</v>
       </c>
       <c r="F29">
-        <v>2.6541</v>
+        <v>2.7524</v>
       </c>
       <c r="G29">
         <v>2.29</v>
@@ -3665,28 +3665,28 @@
         <v>1.123</v>
       </c>
       <c r="M29">
-        <v>0.14199435</v>
+        <v>0.1472534</v>
       </c>
       <c r="N29">
-        <v>0.98100565</v>
+        <v>0.9757466</v>
       </c>
       <c r="O29">
-        <v>0.2452514125</v>
+        <v>0.24393665</v>
       </c>
       <c r="P29">
-        <v>0.7357542374999999</v>
+        <v>0.73180995</v>
       </c>
       <c r="Q29">
-        <v>1.0727542375</v>
+        <v>1.06880995</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1272948294885125</v>
+        <v>0.1282051828116639</v>
       </c>
       <c r="T29">
-        <v>0.7881172862173905</v>
+        <v>0.7969210986192827</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.908765383974785</v>
+        <v>7.626309477404257</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.103542731624398</v>
+        <v>0.1035004877221818</v>
       </c>
       <c r="C30">
-        <v>7.457539249250877</v>
+        <v>7.36171766063179</v>
       </c>
       <c r="D30">
-        <v>7.919939249250875</v>
+        <v>7.92241766063179</v>
       </c>
       <c r="E30">
-        <v>2.2624</v>
+        <v>2.3607</v>
       </c>
       <c r="F30">
-        <v>2.7524</v>
+        <v>2.8507</v>
       </c>
       <c r="G30">
         <v>2.29</v>
@@ -3747,45 +3747,45 @@
         <v>1.123</v>
       </c>
       <c r="M30">
-        <v>0.1472534</v>
+        <v>0.15479301</v>
       </c>
       <c r="N30">
-        <v>0.9757466</v>
+        <v>0.96820699</v>
       </c>
       <c r="O30">
-        <v>0.24393665</v>
+        <v>0.2420517475</v>
       </c>
       <c r="P30">
-        <v>0.73180995</v>
+        <v>0.7261552425</v>
       </c>
       <c r="Q30">
-        <v>1.06880995</v>
+        <v>1.0631552425</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1282051828116639</v>
+        <v>0.129141179890397</v>
       </c>
       <c r="T30">
-        <v>0.7969210986192827</v>
+        <v>0.8059729057367211</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.626309477404257</v>
+        <v>7.254849556837224</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1035004877221818</v>
+        <v>0.1032902438199657</v>
       </c>
       <c r="C31">
-        <v>7.36171766063179</v>
+        <v>7.275775586133465</v>
       </c>
       <c r="D31">
-        <v>7.92241766063179</v>
+        <v>7.934775586133465</v>
       </c>
       <c r="E31">
-        <v>2.3607</v>
+        <v>2.459</v>
       </c>
       <c r="F31">
-        <v>2.8507</v>
+        <v>2.949</v>
       </c>
       <c r="G31">
         <v>2.29</v>
@@ -3829,28 +3829,28 @@
         <v>1.123</v>
       </c>
       <c r="M31">
-        <v>0.15479301</v>
+        <v>0.1601307</v>
       </c>
       <c r="N31">
-        <v>0.96820699</v>
+        <v>0.9628693</v>
       </c>
       <c r="O31">
-        <v>0.2420517475</v>
+        <v>0.240717325</v>
       </c>
       <c r="P31">
-        <v>0.7261552425</v>
+        <v>0.7221519750000001</v>
       </c>
       <c r="Q31">
-        <v>1.0631552425</v>
+        <v>1.059151975</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.129141179890397</v>
+        <v>0.1301039197428082</v>
       </c>
       <c r="T31">
-        <v>0.8059729057367211</v>
+        <v>0.8152833359146578</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.254849556837224</v>
+        <v>7.013021238275984</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1032902438199657</v>
+        <v>0.1030799999177496</v>
       </c>
       <c r="C32">
-        <v>7.275775586133465</v>
+        <v>7.189872125331577</v>
       </c>
       <c r="D32">
-        <v>7.934775586133465</v>
+        <v>7.947172125331577</v>
       </c>
       <c r="E32">
-        <v>2.459</v>
+        <v>2.5573</v>
       </c>
       <c r="F32">
-        <v>2.949</v>
+        <v>3.0473</v>
       </c>
       <c r="G32">
         <v>2.29</v>
@@ -3911,28 +3911,28 @@
         <v>1.123</v>
       </c>
       <c r="M32">
-        <v>0.1601307</v>
+        <v>0.16546839</v>
       </c>
       <c r="N32">
-        <v>0.9628693</v>
+        <v>0.95753161</v>
       </c>
       <c r="O32">
-        <v>0.240717325</v>
+        <v>0.2393829025</v>
       </c>
       <c r="P32">
-        <v>0.7221519750000001</v>
+        <v>0.7181487074999999</v>
       </c>
       <c r="Q32">
-        <v>1.059151975</v>
+        <v>1.0551487075</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1301039197428082</v>
+        <v>0.1310945650981878</v>
       </c>
       <c r="T32">
-        <v>0.8152833359146578</v>
+        <v>0.824863633633984</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.013021238275984</v>
+        <v>6.786794746718694</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1030799999177496</v>
+        <v>0.1028697560155335</v>
       </c>
       <c r="C33">
-        <v>7.189872125331577</v>
+        <v>7.10400745948842</v>
       </c>
       <c r="D33">
-        <v>7.947172125331577</v>
+        <v>7.95960745948842</v>
       </c>
       <c r="E33">
-        <v>2.5573</v>
+        <v>2.6556</v>
       </c>
       <c r="F33">
-        <v>3.0473</v>
+        <v>3.1456</v>
       </c>
       <c r="G33">
         <v>2.29</v>
@@ -3993,28 +3993,28 @@
         <v>1.123</v>
       </c>
       <c r="M33">
-        <v>0.16546839</v>
+        <v>0.17080608</v>
       </c>
       <c r="N33">
-        <v>0.95753161</v>
+        <v>0.95219392</v>
       </c>
       <c r="O33">
-        <v>0.2393829025</v>
+        <v>0.23804848</v>
       </c>
       <c r="P33">
-        <v>0.7181487074999999</v>
+        <v>0.71414544</v>
       </c>
       <c r="Q33">
-        <v>1.0551487075</v>
+        <v>1.05114544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1310945650981878</v>
+        <v>0.1321143470816669</v>
       </c>
       <c r="T33">
-        <v>0.824863633633984</v>
+        <v>0.8347257048156433</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.786794746718694</v>
+        <v>6.574707410883734</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1028697560155335</v>
+        <v>0.1026595121133174</v>
       </c>
       <c r="C34">
-        <v>7.10400745948842</v>
+        <v>7.018181771002588</v>
       </c>
       <c r="D34">
-        <v>7.95960745948842</v>
+        <v>7.972081771002587</v>
       </c>
       <c r="E34">
-        <v>2.6556</v>
+        <v>2.7539</v>
       </c>
       <c r="F34">
-        <v>3.1456</v>
+        <v>3.2439</v>
       </c>
       <c r="G34">
         <v>2.29</v>
@@ -4075,28 +4075,28 @@
         <v>1.123</v>
       </c>
       <c r="M34">
-        <v>0.17080608</v>
+        <v>0.17614377</v>
       </c>
       <c r="N34">
-        <v>0.95219392</v>
+        <v>0.94685623</v>
       </c>
       <c r="O34">
-        <v>0.23804848</v>
+        <v>0.2367140575</v>
       </c>
       <c r="P34">
-        <v>0.71414544</v>
+        <v>0.7101421725</v>
       </c>
       <c r="Q34">
-        <v>1.05114544</v>
+        <v>1.0471421725</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1321143470816669</v>
+        <v>0.1331645703183841</v>
       </c>
       <c r="T34">
-        <v>0.8347257048156433</v>
+        <v>0.8448821661818299</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.574707410883734</v>
+        <v>6.375473852978167</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1026595121133174</v>
+        <v>0.1024492682111012</v>
       </c>
       <c r="C35">
-        <v>7.018181771002588</v>
+        <v>6.932395243417888</v>
       </c>
       <c r="D35">
-        <v>7.972081771002587</v>
+        <v>7.984595243417889</v>
       </c>
       <c r="E35">
-        <v>2.7539</v>
+        <v>2.8522</v>
       </c>
       <c r="F35">
-        <v>3.2439</v>
+        <v>3.3422</v>
       </c>
       <c r="G35">
         <v>2.29</v>
@@ -4157,28 +4157,28 @@
         <v>1.123</v>
       </c>
       <c r="M35">
-        <v>0.17614377</v>
+        <v>0.18148146</v>
       </c>
       <c r="N35">
-        <v>0.94685623</v>
+        <v>0.94151854</v>
       </c>
       <c r="O35">
-        <v>0.2367140575</v>
+        <v>0.235379635</v>
       </c>
       <c r="P35">
-        <v>0.7101421725</v>
+        <v>0.706138905</v>
       </c>
       <c r="Q35">
-        <v>1.0471421725</v>
+        <v>1.043138905</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1331645703183841</v>
+        <v>0.1342466185016686</v>
       </c>
       <c r="T35">
-        <v>0.8448821661818299</v>
+        <v>0.8553463991045673</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.375473852978167</v>
+        <v>6.187959916125868</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1024492682111012</v>
+        <v>0.1025015243088851</v>
       </c>
       <c r="C36">
-        <v>6.932395243417888</v>
+        <v>6.830981354137711</v>
       </c>
       <c r="D36">
-        <v>7.984595243417889</v>
+        <v>7.981481354137711</v>
       </c>
       <c r="E36">
-        <v>2.8522</v>
+        <v>2.950500000000001</v>
       </c>
       <c r="F36">
-        <v>3.3422</v>
+        <v>3.440500000000001</v>
       </c>
       <c r="G36">
         <v>2.29</v>
@@ -4239,45 +4239,45 @@
         <v>1.123</v>
       </c>
       <c r="M36">
-        <v>0.18148146</v>
+        <v>0.19025965</v>
       </c>
       <c r="N36">
-        <v>0.94151854</v>
+        <v>0.93274035</v>
       </c>
       <c r="O36">
-        <v>0.235379635</v>
+        <v>0.2331850875</v>
       </c>
       <c r="P36">
-        <v>0.706138905</v>
+        <v>0.6995552625</v>
       </c>
       <c r="Q36">
-        <v>1.043138905</v>
+        <v>1.0365552625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1342466185016686</v>
+        <v>0.1353619604752079</v>
       </c>
       <c r="T36">
-        <v>0.8553463991045673</v>
+        <v>0.8661326084249276</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.187959916125868</v>
+        <v>5.902460138027164</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1025015243088851</v>
+        <v>0.102298780406669</v>
       </c>
       <c r="C37">
-        <v>6.830981354137711</v>
+        <v>6.744776252083172</v>
       </c>
       <c r="D37">
-        <v>7.981481354137711</v>
+        <v>7.993576252083171</v>
       </c>
       <c r="E37">
-        <v>2.950500000000001</v>
+        <v>3.048800000000001</v>
       </c>
       <c r="F37">
-        <v>3.440500000000001</v>
+        <v>3.538800000000001</v>
       </c>
       <c r="G37">
         <v>2.29</v>
@@ -4321,28 +4321,28 @@
         <v>1.123</v>
       </c>
       <c r="M37">
-        <v>0.19025965</v>
+        <v>0.19569564</v>
       </c>
       <c r="N37">
-        <v>0.93274035</v>
+        <v>0.9273043599999999</v>
       </c>
       <c r="O37">
-        <v>0.2331850875</v>
+        <v>0.23182609</v>
       </c>
       <c r="P37">
-        <v>0.6995552625</v>
+        <v>0.69547827</v>
       </c>
       <c r="Q37">
-        <v>1.0365552625</v>
+        <v>1.03247827</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1353619604752079</v>
+        <v>0.1365121568854203</v>
       </c>
       <c r="T37">
-        <v>0.8661326084249276</v>
+        <v>0.8772558867865491</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.902460138027164</v>
+        <v>5.738502911970853</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.102298780406669</v>
+        <v>0.1020960365044529</v>
       </c>
       <c r="C38">
-        <v>6.744776252083168</v>
+        <v>6.658607862153737</v>
       </c>
       <c r="D38">
-        <v>7.993576252083169</v>
+        <v>8.005707862153738</v>
       </c>
       <c r="E38">
-        <v>3.0488</v>
+        <v>3.1471</v>
       </c>
       <c r="F38">
-        <v>3.5388</v>
+        <v>3.6371</v>
       </c>
       <c r="G38">
         <v>2.29</v>
@@ -4403,28 +4403,28 @@
         <v>1.123</v>
       </c>
       <c r="M38">
-        <v>0.19569564</v>
+        <v>0.20113163</v>
       </c>
       <c r="N38">
-        <v>0.9273043599999999</v>
+        <v>0.92186837</v>
       </c>
       <c r="O38">
-        <v>0.23182609</v>
+        <v>0.2304670925</v>
       </c>
       <c r="P38">
-        <v>0.69547827</v>
+        <v>0.6914012775</v>
       </c>
       <c r="Q38">
-        <v>1.03247827</v>
+        <v>1.0284012775</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1365121568854203</v>
+        <v>0.1376988674673855</v>
       </c>
       <c r="T38">
-        <v>0.8772558867865491</v>
+        <v>0.8887322850961585</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.738502911970854</v>
+        <v>5.583408238674345</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1020960365044529</v>
+        <v>0.1018932926022367</v>
       </c>
       <c r="C39">
-        <v>6.658607862153737</v>
+        <v>6.572476351754142</v>
       </c>
       <c r="D39">
-        <v>8.005707862153738</v>
+        <v>8.017876351754143</v>
       </c>
       <c r="E39">
-        <v>3.1471</v>
+        <v>3.2454</v>
       </c>
       <c r="F39">
-        <v>3.6371</v>
+        <v>3.7354</v>
       </c>
       <c r="G39">
         <v>2.29</v>
@@ -4485,28 +4485,28 @@
         <v>1.123</v>
       </c>
       <c r="M39">
-        <v>0.20113163</v>
+        <v>0.20656762</v>
       </c>
       <c r="N39">
-        <v>0.92186837</v>
+        <v>0.9164323799999999</v>
       </c>
       <c r="O39">
-        <v>0.2304670925</v>
+        <v>0.229108095</v>
       </c>
       <c r="P39">
-        <v>0.6914012775</v>
+        <v>0.687324285</v>
       </c>
       <c r="Q39">
-        <v>1.0284012775</v>
+        <v>1.024324285</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1376988674673855</v>
+        <v>0.1389238590358657</v>
       </c>
       <c r="T39">
-        <v>0.8887322850961585</v>
+        <v>0.9005788898028522</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.583408238674345</v>
+        <v>5.436476442919756</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1018932926022367</v>
+        <v>0.1016905487000206</v>
       </c>
       <c r="C40">
-        <v>6.572476351754142</v>
+        <v>6.486381889308465</v>
       </c>
       <c r="D40">
-        <v>8.017876351754143</v>
+        <v>8.030081889308464</v>
       </c>
       <c r="E40">
-        <v>3.2454</v>
+        <v>3.3437</v>
       </c>
       <c r="F40">
-        <v>3.7354</v>
+        <v>3.8337</v>
       </c>
       <c r="G40">
         <v>2.29</v>
@@ -4567,28 +4567,28 @@
         <v>1.123</v>
       </c>
       <c r="M40">
-        <v>0.20656762</v>
+        <v>0.21200361</v>
       </c>
       <c r="N40">
-        <v>0.9164323799999999</v>
+        <v>0.91099639</v>
       </c>
       <c r="O40">
-        <v>0.229108095</v>
+        <v>0.2277490975</v>
       </c>
       <c r="P40">
-        <v>0.687324285</v>
+        <v>0.6832472924999999</v>
       </c>
       <c r="Q40">
-        <v>1.024324285</v>
+        <v>1.0202472925</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1389238590358657</v>
+        <v>0.1401890142623289</v>
       </c>
       <c r="T40">
-        <v>0.9005788898028522</v>
+        <v>0.9128139077786178</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.436476442919756</v>
+        <v>5.297079611050019</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1016905487000206</v>
+        <v>0.1014878047978045</v>
       </c>
       <c r="C41">
-        <v>6.486381889308465</v>
+        <v>6.40032464426791</v>
       </c>
       <c r="D41">
-        <v>8.030081889308464</v>
+        <v>8.042324644267909</v>
       </c>
       <c r="E41">
-        <v>3.3437</v>
+        <v>3.442</v>
       </c>
       <c r="F41">
-        <v>3.8337</v>
+        <v>3.932</v>
       </c>
       <c r="G41">
         <v>2.29</v>
@@ -4649,28 +4649,28 @@
         <v>1.123</v>
       </c>
       <c r="M41">
-        <v>0.21200361</v>
+        <v>0.2174396</v>
       </c>
       <c r="N41">
-        <v>0.91099639</v>
+        <v>0.9055603999999999</v>
       </c>
       <c r="O41">
-        <v>0.2277490975</v>
+        <v>0.2263901</v>
       </c>
       <c r="P41">
-        <v>0.6832472924999999</v>
+        <v>0.6791703</v>
       </c>
       <c r="Q41">
-        <v>1.0202472925</v>
+        <v>1.0161703</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1401890142623289</v>
+        <v>0.1414963413296742</v>
       </c>
       <c r="T41">
-        <v>0.9128139077786178</v>
+        <v>0.9254567596869089</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.297079611050019</v>
+        <v>5.164652620773768</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1014878047978045</v>
+        <v>0.1012850608955884</v>
       </c>
       <c r="C42">
-        <v>6.40032464426791</v>
+        <v>6.314304787118651</v>
       </c>
       <c r="D42">
-        <v>8.042324644267909</v>
+        <v>8.054604787118652</v>
       </c>
       <c r="E42">
-        <v>3.442</v>
+        <v>3.5403</v>
       </c>
       <c r="F42">
-        <v>3.932</v>
+        <v>4.0303</v>
       </c>
       <c r="G42">
         <v>2.29</v>
@@ -4731,28 +4731,28 @@
         <v>1.123</v>
       </c>
       <c r="M42">
-        <v>0.2174396</v>
+        <v>0.22287559</v>
       </c>
       <c r="N42">
-        <v>0.9055603999999999</v>
+        <v>0.90012441</v>
       </c>
       <c r="O42">
-        <v>0.2263901</v>
+        <v>0.2250311025</v>
       </c>
       <c r="P42">
-        <v>0.6791703</v>
+        <v>0.6750933075</v>
       </c>
       <c r="Q42">
-        <v>1.0161703</v>
+        <v>1.0120933075</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1414963413296742</v>
+        <v>0.1428479845687939</v>
       </c>
       <c r="T42">
-        <v>0.9254567596869089</v>
+        <v>0.9385281828463286</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.164652620773768</v>
+        <v>5.038685483681725</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1012850608955884</v>
+        <v>0.1010823169933723</v>
       </c>
       <c r="C43">
-        <v>6.314304787118651</v>
+        <v>6.228322489389745</v>
       </c>
       <c r="D43">
-        <v>8.054604787118652</v>
+        <v>8.066922489389746</v>
       </c>
       <c r="E43">
-        <v>3.5403</v>
+        <v>3.6386</v>
       </c>
       <c r="F43">
-        <v>4.0303</v>
+        <v>4.1286</v>
       </c>
       <c r="G43">
         <v>2.29</v>
@@ -4813,28 +4813,28 @@
         <v>1.123</v>
       </c>
       <c r="M43">
-        <v>0.22287559</v>
+        <v>0.22831158</v>
       </c>
       <c r="N43">
-        <v>0.90012441</v>
+        <v>0.8946884199999999</v>
       </c>
       <c r="O43">
-        <v>0.2250311025</v>
+        <v>0.223672105</v>
       </c>
       <c r="P43">
-        <v>0.6750933075</v>
+        <v>0.6710163149999999</v>
       </c>
       <c r="Q43">
-        <v>1.0120933075</v>
+        <v>1.008016315</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1428479845687939</v>
+        <v>0.1442462361954694</v>
       </c>
       <c r="T43">
-        <v>0.9385281828463286</v>
+        <v>0.9520503447353833</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.038685483681725</v>
+        <v>4.918716781689302</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1010823169933723</v>
+        <v>0.1008795730911561</v>
       </c>
       <c r="C44">
-        <v>6.228322489389746</v>
+        <v>6.142377923661113</v>
       </c>
       <c r="D44">
-        <v>8.066922489389745</v>
+        <v>8.079277923661113</v>
       </c>
       <c r="E44">
-        <v>3.638599999999999</v>
+        <v>3.736899999999999</v>
       </c>
       <c r="F44">
-        <v>4.1286</v>
+        <v>4.2269</v>
       </c>
       <c r="G44">
         <v>2.29</v>
@@ -4895,28 +4895,28 @@
         <v>1.123</v>
       </c>
       <c r="M44">
-        <v>0.22831158</v>
+        <v>0.23374757</v>
       </c>
       <c r="N44">
-        <v>0.89468842</v>
+        <v>0.88925243</v>
       </c>
       <c r="O44">
-        <v>0.223672105</v>
+        <v>0.2223131075</v>
       </c>
       <c r="P44">
-        <v>0.671016315</v>
+        <v>0.6669393225</v>
       </c>
       <c r="Q44">
-        <v>1.008016315</v>
+        <v>1.0039393225</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1442462361954694</v>
+        <v>0.14569354928273</v>
       </c>
       <c r="T44">
-        <v>0.9520503447353833</v>
+        <v>0.9660469684451065</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.918716781689304</v>
+        <v>4.804328019324436</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1008795730911561</v>
+        <v>0.10067682918894</v>
       </c>
       <c r="C45">
-        <v>6.142377923661113</v>
+        <v>6.056471263571601</v>
       </c>
       <c r="D45">
-        <v>8.079277923661113</v>
+        <v>8.0916712635716</v>
       </c>
       <c r="E45">
-        <v>3.736899999999999</v>
+        <v>3.835199999999999</v>
       </c>
       <c r="F45">
-        <v>4.2269</v>
+        <v>4.3252</v>
       </c>
       <c r="G45">
         <v>2.29</v>
@@ -4977,28 +4977,28 @@
         <v>1.123</v>
       </c>
       <c r="M45">
-        <v>0.23374757</v>
+        <v>0.23918356</v>
       </c>
       <c r="N45">
-        <v>0.88925243</v>
+        <v>0.88381644</v>
       </c>
       <c r="O45">
-        <v>0.2223131075</v>
+        <v>0.22095411</v>
       </c>
       <c r="P45">
-        <v>0.6669393225</v>
+        <v>0.6628623300000001</v>
       </c>
       <c r="Q45">
-        <v>1.0039393225</v>
+        <v>0.99986233</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.14569354928273</v>
+        <v>0.1471925521231072</v>
       </c>
       <c r="T45">
-        <v>0.9660469684451065</v>
+        <v>0.9805434715730345</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.804328019324436</v>
+        <v>4.695138746157972</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.10067682918894</v>
+        <v>0.1004740852867239</v>
       </c>
       <c r="C46">
-        <v>6.056471263571601</v>
+        <v>5.970602683827122</v>
       </c>
       <c r="D46">
-        <v>8.0916712635716</v>
+        <v>8.10410268382712</v>
       </c>
       <c r="E46">
-        <v>3.835199999999999</v>
+        <v>3.9335</v>
       </c>
       <c r="F46">
-        <v>4.3252</v>
+        <v>4.4235</v>
       </c>
       <c r="G46">
         <v>2.29</v>
@@ -5059,28 +5059,28 @@
         <v>1.123</v>
       </c>
       <c r="M46">
-        <v>0.23918356</v>
+        <v>0.24461955</v>
       </c>
       <c r="N46">
-        <v>0.88381644</v>
+        <v>0.87838045</v>
       </c>
       <c r="O46">
-        <v>0.22095411</v>
+        <v>0.2195951125</v>
       </c>
       <c r="P46">
-        <v>0.6628623300000001</v>
+        <v>0.6587853375</v>
       </c>
       <c r="Q46">
-        <v>0.99986233</v>
+        <v>0.9957853375000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1471925521231072</v>
+        <v>0.1487460641576798</v>
       </c>
       <c r="T46">
-        <v>0.9805434715730345</v>
+        <v>0.9955671202692504</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.695138746157972</v>
+        <v>4.590802329576683</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1004740852867239</v>
+        <v>0.1011338413845078</v>
       </c>
       <c r="C47">
-        <v>5.970602683827122</v>
+        <v>5.831988556692663</v>
       </c>
       <c r="D47">
-        <v>8.10410268382712</v>
+        <v>8.063788556692664</v>
       </c>
       <c r="E47">
-        <v>3.9335</v>
+        <v>4.0318</v>
       </c>
       <c r="F47">
-        <v>4.4235</v>
+        <v>4.5218</v>
       </c>
       <c r="G47">
         <v>2.29</v>
@@ -5141,45 +5141,45 @@
         <v>1.123</v>
       </c>
       <c r="M47">
-        <v>0.24461955</v>
+        <v>0.26136004</v>
       </c>
       <c r="N47">
-        <v>0.87838045</v>
+        <v>0.86163996</v>
       </c>
       <c r="O47">
-        <v>0.2195951125</v>
+        <v>0.21540999</v>
       </c>
       <c r="P47">
-        <v>0.6587853375</v>
+        <v>0.64622997</v>
       </c>
       <c r="Q47">
-        <v>0.9957853375000001</v>
+        <v>0.98322997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1487460641576798</v>
+        <v>0.1503571136750144</v>
       </c>
       <c r="T47">
-        <v>0.9955671202692504</v>
+        <v>1.01114720039866</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.590802329576683</v>
+        <v>4.296754775519624</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1011338413845078</v>
+        <v>0.1009498474822916</v>
       </c>
       <c r="C48">
-        <v>5.831988556692663</v>
+        <v>5.744891042244523</v>
       </c>
       <c r="D48">
-        <v>8.063788556692664</v>
+        <v>8.074991042244521</v>
       </c>
       <c r="E48">
-        <v>4.0318</v>
+        <v>4.1301</v>
       </c>
       <c r="F48">
-        <v>4.5218</v>
+        <v>4.6201</v>
       </c>
       <c r="G48">
         <v>2.29</v>
@@ -5223,28 +5223,28 @@
         <v>1.123</v>
       </c>
       <c r="M48">
-        <v>0.26136004</v>
+        <v>0.26704178</v>
       </c>
       <c r="N48">
-        <v>0.86163996</v>
+        <v>0.85595822</v>
       </c>
       <c r="O48">
-        <v>0.21540999</v>
+        <v>0.213989555</v>
       </c>
       <c r="P48">
-        <v>0.64622997</v>
+        <v>0.641968665</v>
       </c>
       <c r="Q48">
-        <v>0.98322997</v>
+        <v>0.978968665</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1503571136750144</v>
+        <v>0.1520289575137578</v>
       </c>
       <c r="T48">
-        <v>1.01114720039866</v>
+        <v>1.027315208080122</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.296754775519624</v>
+        <v>4.205334461146866</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1009498474822916</v>
+        <v>0.1007658535800755</v>
       </c>
       <c r="C49">
-        <v>5.744891042244523</v>
+        <v>5.657824696834853</v>
       </c>
       <c r="D49">
-        <v>8.074991042244521</v>
+        <v>8.086224696834853</v>
       </c>
       <c r="E49">
-        <v>4.1301</v>
+        <v>4.228400000000001</v>
       </c>
       <c r="F49">
-        <v>4.6201</v>
+        <v>4.718400000000001</v>
       </c>
       <c r="G49">
         <v>2.29</v>
@@ -5305,28 +5305,28 @@
         <v>1.123</v>
       </c>
       <c r="M49">
-        <v>0.26704178</v>
+        <v>0.2727235200000001</v>
       </c>
       <c r="N49">
-        <v>0.85595822</v>
+        <v>0.85027648</v>
       </c>
       <c r="O49">
-        <v>0.213989555</v>
+        <v>0.21256912</v>
       </c>
       <c r="P49">
-        <v>0.641968665</v>
+        <v>0.6377073600000001</v>
       </c>
       <c r="Q49">
-        <v>0.978968665</v>
+        <v>0.97470736</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1520289575137578</v>
+        <v>0.1537651030386068</v>
       </c>
       <c r="T49">
-        <v>1.027315208080122</v>
+        <v>1.044105062210872</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.205334461146866</v>
+        <v>4.11772332653964</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1007658535800755</v>
+        <v>0.1005818596778594</v>
       </c>
       <c r="C50">
-        <v>5.657824696834854</v>
+        <v>5.570789650728824</v>
       </c>
       <c r="D50">
-        <v>8.086224696834853</v>
+        <v>8.097489650728823</v>
       </c>
       <c r="E50">
-        <v>4.2284</v>
+        <v>4.3267</v>
       </c>
       <c r="F50">
-        <v>4.7184</v>
+        <v>4.8167</v>
       </c>
       <c r="G50">
         <v>2.29</v>
@@ -5387,28 +5387,28 @@
         <v>1.123</v>
       </c>
       <c r="M50">
-        <v>0.27272352</v>
+        <v>0.27840526</v>
       </c>
       <c r="N50">
-        <v>0.85027648</v>
+        <v>0.84459474</v>
       </c>
       <c r="O50">
-        <v>0.21256912</v>
+        <v>0.211148685</v>
       </c>
       <c r="P50">
-        <v>0.6377073600000001</v>
+        <v>0.6334460550000001</v>
       </c>
       <c r="Q50">
-        <v>0.97470736</v>
+        <v>0.970446055</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1537651030386068</v>
+        <v>0.1555693327016851</v>
       </c>
       <c r="T50">
-        <v>1.044105062210872</v>
+        <v>1.061553341993807</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.11772332653964</v>
+        <v>4.033688156610259</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1005818596778594</v>
+        <v>0.1017103657756433</v>
       </c>
       <c r="C51">
-        <v>5.570789650728824</v>
+        <v>5.403887228324733</v>
       </c>
       <c r="D51">
-        <v>8.097489650728823</v>
+        <v>8.028887228324734</v>
       </c>
       <c r="E51">
-        <v>4.3267</v>
+        <v>4.425</v>
       </c>
       <c r="F51">
-        <v>4.8167</v>
+        <v>4.915</v>
       </c>
       <c r="G51">
         <v>2.29</v>
@@ -5469,45 +5469,45 @@
         <v>1.123</v>
       </c>
       <c r="M51">
-        <v>0.27840526</v>
+        <v>0.3012895</v>
       </c>
       <c r="N51">
-        <v>0.84459474</v>
+        <v>0.8217105</v>
       </c>
       <c r="O51">
-        <v>0.211148685</v>
+        <v>0.205427625</v>
       </c>
       <c r="P51">
-        <v>0.6334460550000001</v>
+        <v>0.616282875</v>
       </c>
       <c r="Q51">
-        <v>0.970446055</v>
+        <v>0.953282875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1555693327016851</v>
+        <v>0.1574457315512865</v>
       </c>
       <c r="T51">
-        <v>1.061553341993807</v>
+        <v>1.07969955296806</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.033688156610259</v>
+        <v>3.727312103475229</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1017103657756433</v>
+        <v>0.1015526218734271</v>
       </c>
       <c r="C52">
-        <v>5.403887228324733</v>
+        <v>5.315106586959605</v>
       </c>
       <c r="D52">
-        <v>8.028887228324734</v>
+        <v>8.038406586959606</v>
       </c>
       <c r="E52">
-        <v>4.425</v>
+        <v>4.5233</v>
       </c>
       <c r="F52">
-        <v>4.915</v>
+        <v>5.0133</v>
       </c>
       <c r="G52">
         <v>2.29</v>
@@ -5551,28 +5551,28 @@
         <v>1.123</v>
       </c>
       <c r="M52">
-        <v>0.3012895</v>
+        <v>0.30731529</v>
       </c>
       <c r="N52">
-        <v>0.8217105</v>
+        <v>0.81568471</v>
       </c>
       <c r="O52">
-        <v>0.205427625</v>
+        <v>0.2039211775</v>
       </c>
       <c r="P52">
-        <v>0.616282875</v>
+        <v>0.6117635324999999</v>
       </c>
       <c r="Q52">
-        <v>0.953282875</v>
+        <v>0.9487635324999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1574457315512865</v>
+        <v>0.159398718109035</v>
       </c>
       <c r="T52">
-        <v>1.07969955296806</v>
+        <v>1.098586425614732</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.727312103475229</v>
+        <v>3.654227552426695</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1015526218734271</v>
+        <v>0.101394877971211</v>
       </c>
       <c r="C53">
-        <v>5.315106586959605</v>
+        <v>5.226348545427856</v>
       </c>
       <c r="D53">
-        <v>8.038406586959606</v>
+        <v>8.047948545427856</v>
       </c>
       <c r="E53">
-        <v>4.5233</v>
+        <v>4.6216</v>
       </c>
       <c r="F53">
-        <v>5.0133</v>
+        <v>5.1116</v>
       </c>
       <c r="G53">
         <v>2.29</v>
@@ -5633,28 +5633,28 @@
         <v>1.123</v>
       </c>
       <c r="M53">
-        <v>0.30731529</v>
+        <v>0.31334108</v>
       </c>
       <c r="N53">
-        <v>0.81568471</v>
+        <v>0.8096589199999999</v>
       </c>
       <c r="O53">
-        <v>0.2039211775</v>
+        <v>0.20241473</v>
       </c>
       <c r="P53">
-        <v>0.6117635324999999</v>
+        <v>0.60724419</v>
       </c>
       <c r="Q53">
-        <v>0.9487635324999999</v>
+        <v>0.94424419</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.159398718109035</v>
+        <v>0.1614330791066896</v>
       </c>
       <c r="T53">
-        <v>1.098586425614732</v>
+        <v>1.118260251288348</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.654227552426695</v>
+        <v>3.583953945649259</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.101394877971211</v>
+        <v>0.1012371340689949</v>
       </c>
       <c r="C54">
-        <v>5.226348545427856</v>
+        <v>5.137613184306251</v>
       </c>
       <c r="D54">
-        <v>8.047948545427856</v>
+        <v>8.057513184306252</v>
       </c>
       <c r="E54">
-        <v>4.6216</v>
+        <v>4.7199</v>
       </c>
       <c r="F54">
-        <v>5.1116</v>
+        <v>5.2099</v>
       </c>
       <c r="G54">
         <v>2.29</v>
@@ -5715,28 +5715,28 @@
         <v>1.123</v>
       </c>
       <c r="M54">
-        <v>0.31334108</v>
+        <v>0.31936687</v>
       </c>
       <c r="N54">
-        <v>0.8096589199999999</v>
+        <v>0.8036331299999999</v>
       </c>
       <c r="O54">
-        <v>0.20241473</v>
+        <v>0.2009082825</v>
       </c>
       <c r="P54">
-        <v>0.60724419</v>
+        <v>0.6027248475</v>
       </c>
       <c r="Q54">
-        <v>0.94424419</v>
+        <v>0.9397248475</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1614330791066896</v>
+        <v>0.163554008657436</v>
       </c>
       <c r="T54">
-        <v>1.118260251288348</v>
+        <v>1.138771261033182</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.583953945649259</v>
+        <v>3.516332173089838</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1012371340689949</v>
+        <v>0.1022133901667788</v>
       </c>
       <c r="C55">
-        <v>5.137613184306251</v>
+        <v>4.980481273036193</v>
       </c>
       <c r="D55">
-        <v>8.057513184306252</v>
+        <v>7.998681273036194</v>
       </c>
       <c r="E55">
-        <v>4.7199</v>
+        <v>4.8182</v>
       </c>
       <c r="F55">
-        <v>5.2099</v>
+        <v>5.3082</v>
       </c>
       <c r="G55">
         <v>2.29</v>
@@ -5797,45 +5797,45 @@
         <v>1.123</v>
       </c>
       <c r="M55">
-        <v>0.31936687</v>
+        <v>0.34025562</v>
       </c>
       <c r="N55">
-        <v>0.8036331299999999</v>
+        <v>0.78274438</v>
       </c>
       <c r="O55">
-        <v>0.2009082825</v>
+        <v>0.195686095</v>
       </c>
       <c r="P55">
-        <v>0.6027248475</v>
+        <v>0.587058285</v>
       </c>
       <c r="Q55">
-        <v>0.9397248475</v>
+        <v>0.9240582850000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.163554008657436</v>
+        <v>0.1657671525364756</v>
       </c>
       <c r="T55">
-        <v>1.138771261033182</v>
+        <v>1.1601740538104</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.516332173089838</v>
+        <v>3.300459813125203</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1022133901667788</v>
+        <v>0.1020766462645627</v>
       </c>
       <c r="C56">
-        <v>4.980481273036193</v>
+        <v>4.890370047731431</v>
       </c>
       <c r="D56">
-        <v>7.998681273036194</v>
+        <v>8.006870047731432</v>
       </c>
       <c r="E56">
-        <v>4.8182</v>
+        <v>4.9165</v>
       </c>
       <c r="F56">
-        <v>5.3082</v>
+        <v>5.4065</v>
       </c>
       <c r="G56">
         <v>2.29</v>
@@ -5879,28 +5879,28 @@
         <v>1.123</v>
       </c>
       <c r="M56">
-        <v>0.34025562</v>
+        <v>0.34655665</v>
       </c>
       <c r="N56">
-        <v>0.78274438</v>
+        <v>0.77644335</v>
       </c>
       <c r="O56">
-        <v>0.195686095</v>
+        <v>0.1941108375</v>
       </c>
       <c r="P56">
-        <v>0.587058285</v>
+        <v>0.5823325125</v>
       </c>
       <c r="Q56">
-        <v>0.9240582850000001</v>
+        <v>0.9193325125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1657671525364756</v>
+        <v>0.1680786583656948</v>
       </c>
       <c r="T56">
-        <v>1.1601740538104</v>
+        <v>1.182528081822162</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.300459813125203</v>
+        <v>3.240451452886563</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1020766462645627</v>
+        <v>0.1019399023623465</v>
       </c>
       <c r="C57">
-        <v>4.890370047731431</v>
+        <v>4.800275606381109</v>
       </c>
       <c r="D57">
-        <v>8.006870047731432</v>
+        <v>8.01507560638111</v>
       </c>
       <c r="E57">
-        <v>4.9165</v>
+        <v>5.0148</v>
       </c>
       <c r="F57">
-        <v>5.4065</v>
+        <v>5.5048</v>
       </c>
       <c r="G57">
         <v>2.29</v>
@@ -5961,28 +5961,28 @@
         <v>1.123</v>
       </c>
       <c r="M57">
-        <v>0.34655665</v>
+        <v>0.3528576800000001</v>
       </c>
       <c r="N57">
-        <v>0.77644335</v>
+        <v>0.7701423199999999</v>
       </c>
       <c r="O57">
-        <v>0.1941108375</v>
+        <v>0.19253558</v>
       </c>
       <c r="P57">
-        <v>0.5823325125</v>
+        <v>0.57760674</v>
       </c>
       <c r="Q57">
-        <v>0.9193325125</v>
+        <v>0.91460674</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1680786583656948</v>
+        <v>0.1704952326416966</v>
       </c>
       <c r="T57">
-        <v>1.182528081822162</v>
+        <v>1.205898202016275</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.240451452886563</v>
+        <v>3.182586248370731</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1019399023623465</v>
+        <v>0.1018031584601304</v>
       </c>
       <c r="C58">
-        <v>4.800275606381109</v>
+        <v>4.710198000639491</v>
       </c>
       <c r="D58">
-        <v>8.01507560638111</v>
+        <v>8.023298000639491</v>
       </c>
       <c r="E58">
-        <v>5.0148</v>
+        <v>5.1131</v>
       </c>
       <c r="F58">
-        <v>5.5048</v>
+        <v>5.6031</v>
       </c>
       <c r="G58">
         <v>2.29</v>
@@ -6043,28 +6043,28 @@
         <v>1.123</v>
       </c>
       <c r="M58">
-        <v>0.3528576800000001</v>
+        <v>0.35915871</v>
       </c>
       <c r="N58">
-        <v>0.7701423199999999</v>
+        <v>0.76384129</v>
       </c>
       <c r="O58">
-        <v>0.19253558</v>
+        <v>0.1909603225</v>
       </c>
       <c r="P58">
-        <v>0.57760674</v>
+        <v>0.5728809674999999</v>
       </c>
       <c r="Q58">
-        <v>0.91460674</v>
+        <v>0.9098809674999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1704952326416966</v>
+        <v>0.1730242057212335</v>
       </c>
       <c r="T58">
-        <v>1.205898202016275</v>
+        <v>1.230355304544999</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.182586248370731</v>
+        <v>3.126751401908086</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1018031584601304</v>
+        <v>0.1016664145579143</v>
       </c>
       <c r="C59">
-        <v>4.710198000639491</v>
+        <v>4.620137282373025</v>
       </c>
       <c r="D59">
-        <v>8.023298000639491</v>
+        <v>8.031537282373025</v>
       </c>
       <c r="E59">
-        <v>5.1131</v>
+        <v>5.2114</v>
       </c>
       <c r="F59">
-        <v>5.6031</v>
+        <v>5.7014</v>
       </c>
       <c r="G59">
         <v>2.29</v>
@@ -6125,28 +6125,28 @@
         <v>1.123</v>
       </c>
       <c r="M59">
-        <v>0.35915871</v>
+        <v>0.36545974</v>
       </c>
       <c r="N59">
-        <v>0.76384129</v>
+        <v>0.75754026</v>
       </c>
       <c r="O59">
-        <v>0.1909603225</v>
+        <v>0.189385065</v>
       </c>
       <c r="P59">
-        <v>0.5728809674999999</v>
+        <v>0.568155195</v>
       </c>
       <c r="Q59">
-        <v>0.9098809674999999</v>
+        <v>0.9051551950000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1730242057212335</v>
+        <v>0.1756736060902721</v>
       </c>
       <c r="T59">
-        <v>1.230355304544999</v>
+        <v>1.255977031003662</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.126751401908086</v>
+        <v>3.072841894978637</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1016664145579143</v>
+        <v>0.1015296706556982</v>
       </c>
       <c r="C60">
-        <v>4.620137282373026</v>
+        <v>4.530093503661432</v>
       </c>
       <c r="D60">
-        <v>8.031537282373025</v>
+        <v>8.03979350366143</v>
       </c>
       <c r="E60">
-        <v>5.211399999999999</v>
+        <v>5.309699999999999</v>
       </c>
       <c r="F60">
-        <v>5.7014</v>
+        <v>5.7997</v>
       </c>
       <c r="G60">
         <v>2.29</v>
@@ -6207,28 +6207,28 @@
         <v>1.123</v>
       </c>
       <c r="M60">
-        <v>0.36545974</v>
+        <v>0.37176077</v>
       </c>
       <c r="N60">
-        <v>0.7575402600000001</v>
+        <v>0.7512392299999999</v>
       </c>
       <c r="O60">
-        <v>0.189385065</v>
+        <v>0.1878098075</v>
       </c>
       <c r="P60">
-        <v>0.5681551950000001</v>
+        <v>0.5634294224999999</v>
       </c>
       <c r="Q60">
-        <v>0.9051551950000001</v>
+        <v>0.9004294225</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1756736060902721</v>
+        <v>0.1784522455017028</v>
       </c>
       <c r="T60">
-        <v>1.255977031003662</v>
+        <v>1.282848597777382</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.072841894978637</v>
+        <v>3.02075982896205</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1015296706556982</v>
+        <v>0.104902926753482</v>
       </c>
       <c r="C61">
-        <v>4.530093503661432</v>
+        <v>4.232958364413825</v>
       </c>
       <c r="D61">
-        <v>8.03979350366143</v>
+        <v>7.840958364413825</v>
       </c>
       <c r="E61">
-        <v>5.309699999999999</v>
+        <v>5.407999999999999</v>
       </c>
       <c r="F61">
-        <v>5.7997</v>
+        <v>5.898</v>
       </c>
       <c r="G61">
         <v>2.29</v>
@@ -6289,45 +6289,45 @@
         <v>1.123</v>
       </c>
       <c r="M61">
-        <v>0.37176077</v>
+        <v>0.4240662</v>
       </c>
       <c r="N61">
-        <v>0.7512392299999999</v>
+        <v>0.6989338</v>
       </c>
       <c r="O61">
-        <v>0.1878098075</v>
+        <v>0.17473345</v>
       </c>
       <c r="P61">
-        <v>0.5634294224999999</v>
+        <v>0.5242003500000001</v>
       </c>
       <c r="Q61">
-        <v>0.9004294225</v>
+        <v>0.8612003500000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1784522455017028</v>
+        <v>0.1813698168837051</v>
       </c>
       <c r="T61">
-        <v>1.282848597777382</v>
+        <v>1.311063742889788</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.02075982896205</v>
+        <v>2.648171441157065</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.104902926753482</v>
+        <v>0.1048246828512659</v>
       </c>
       <c r="C62">
-        <v>4.232958364413825</v>
+        <v>4.139158937146687</v>
       </c>
       <c r="D62">
-        <v>7.840958364413825</v>
+        <v>7.845458937146687</v>
       </c>
       <c r="E62">
-        <v>5.407999999999999</v>
+        <v>5.5063</v>
       </c>
       <c r="F62">
-        <v>5.898</v>
+        <v>5.9963</v>
       </c>
       <c r="G62">
         <v>2.29</v>
@@ -6371,28 +6371,28 @@
         <v>1.123</v>
       </c>
       <c r="M62">
-        <v>0.4240662</v>
+        <v>0.43113397</v>
       </c>
       <c r="N62">
-        <v>0.6989338</v>
+        <v>0.6918660299999999</v>
       </c>
       <c r="O62">
-        <v>0.17473345</v>
+        <v>0.1729665075</v>
       </c>
       <c r="P62">
-        <v>0.5242003500000001</v>
+        <v>0.5188995224999999</v>
       </c>
       <c r="Q62">
-        <v>0.8612003500000001</v>
+        <v>0.8558995224999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1813698168837051</v>
+        <v>0.1844370073109382</v>
       </c>
       <c r="T62">
-        <v>1.311063742889788</v>
+        <v>1.340725818520778</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.648171441157065</v>
+        <v>2.604758794580719</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1048246828512659</v>
+        <v>0.1047464389490498</v>
       </c>
       <c r="C63">
-        <v>4.139158937146687</v>
+        <v>4.045364679346534</v>
       </c>
       <c r="D63">
-        <v>7.845458937146687</v>
+        <v>7.849964679346533</v>
       </c>
       <c r="E63">
-        <v>5.5063</v>
+        <v>5.6046</v>
       </c>
       <c r="F63">
-        <v>5.9963</v>
+        <v>6.0946</v>
       </c>
       <c r="G63">
         <v>2.29</v>
@@ -6453,28 +6453,28 @@
         <v>1.123</v>
       </c>
       <c r="M63">
-        <v>0.43113397</v>
+        <v>0.43820174</v>
       </c>
       <c r="N63">
-        <v>0.6918660299999999</v>
+        <v>0.68479826</v>
       </c>
       <c r="O63">
-        <v>0.1729665075</v>
+        <v>0.171199565</v>
       </c>
       <c r="P63">
-        <v>0.5188995224999999</v>
+        <v>0.513598695</v>
       </c>
       <c r="Q63">
-        <v>0.8558995224999999</v>
+        <v>0.850598695</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1844370073109382</v>
+        <v>0.1876656288132889</v>
       </c>
       <c r="T63">
-        <v>1.340725818520778</v>
+        <v>1.371949056027084</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.604758794580719</v>
+        <v>2.56274655595845</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1047464389490498</v>
+        <v>0.1046681950468337</v>
       </c>
       <c r="C64">
-        <v>4.045364679346534</v>
+        <v>3.951575599925151</v>
       </c>
       <c r="D64">
-        <v>7.849964679346533</v>
+        <v>7.85447559992515</v>
       </c>
       <c r="E64">
-        <v>5.6046</v>
+        <v>5.7029</v>
       </c>
       <c r="F64">
-        <v>6.0946</v>
+        <v>6.1929</v>
       </c>
       <c r="G64">
         <v>2.29</v>
@@ -6535,28 +6535,28 @@
         <v>1.123</v>
       </c>
       <c r="M64">
-        <v>0.43820174</v>
+        <v>0.44526951</v>
       </c>
       <c r="N64">
-        <v>0.68479826</v>
+        <v>0.67773049</v>
       </c>
       <c r="O64">
-        <v>0.171199565</v>
+        <v>0.1694326225</v>
       </c>
       <c r="P64">
-        <v>0.513598695</v>
+        <v>0.5082978674999999</v>
       </c>
       <c r="Q64">
-        <v>0.850598695</v>
+        <v>0.8452978675</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1876656288132889</v>
+        <v>0.1910687703968477</v>
       </c>
       <c r="T64">
-        <v>1.371949056027084</v>
+        <v>1.404860036101299</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.56274655595845</v>
+        <v>2.522068039197204</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1046681950468337</v>
+        <v>0.1064619511446175</v>
       </c>
       <c r="C65">
-        <v>3.951575599925151</v>
+        <v>3.751147883736904</v>
       </c>
       <c r="D65">
-        <v>7.85447559992515</v>
+        <v>7.752347883736904</v>
       </c>
       <c r="E65">
-        <v>5.7029</v>
+        <v>5.8012</v>
       </c>
       <c r="F65">
-        <v>6.1929</v>
+        <v>6.2912</v>
       </c>
       <c r="G65">
         <v>2.29</v>
@@ -6617,45 +6617,45 @@
         <v>1.123</v>
       </c>
       <c r="M65">
-        <v>0.44526951</v>
+        <v>0.47687296</v>
       </c>
       <c r="N65">
-        <v>0.67773049</v>
+        <v>0.64612704</v>
       </c>
       <c r="O65">
-        <v>0.1694326225</v>
+        <v>0.16153176</v>
       </c>
       <c r="P65">
-        <v>0.5082978674999999</v>
+        <v>0.48459528</v>
       </c>
       <c r="Q65">
-        <v>0.8452978675</v>
+        <v>0.8215952799999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1910687703968477</v>
+        <v>0.1946609754017154</v>
       </c>
       <c r="T65">
-        <v>1.404860036101299</v>
+        <v>1.439599403957414</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.522068039197204</v>
+        <v>2.354924883977485</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1064619511446175</v>
+        <v>0.1064129572424014</v>
       </c>
       <c r="C66">
-        <v>3.751147883736904</v>
+        <v>3.655602065408834</v>
       </c>
       <c r="D66">
-        <v>7.752347883736904</v>
+        <v>7.755102065408834</v>
       </c>
       <c r="E66">
-        <v>5.8012</v>
+        <v>5.8995</v>
       </c>
       <c r="F66">
-        <v>6.2912</v>
+        <v>6.3895</v>
       </c>
       <c r="G66">
         <v>2.29</v>
@@ -6699,28 +6699,28 @@
         <v>1.123</v>
       </c>
       <c r="M66">
-        <v>0.47687296</v>
+        <v>0.4843241</v>
       </c>
       <c r="N66">
-        <v>0.64612704</v>
+        <v>0.6386759</v>
       </c>
       <c r="O66">
-        <v>0.16153176</v>
+        <v>0.159668975</v>
       </c>
       <c r="P66">
-        <v>0.48459528</v>
+        <v>0.479006925</v>
       </c>
       <c r="Q66">
-        <v>0.8215952799999999</v>
+        <v>0.8160069249999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1946609754017154</v>
+        <v>0.1984584492640041</v>
       </c>
       <c r="T66">
-        <v>1.439599403957414</v>
+        <v>1.476323878548164</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.354924883977485</v>
+        <v>2.318695270377832</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1064129572424014</v>
+        <v>0.1063639633401853</v>
       </c>
       <c r="C67">
-        <v>3.655602065408834</v>
+        <v>3.560058204736091</v>
       </c>
       <c r="D67">
-        <v>7.755102065408834</v>
+        <v>7.757858204736091</v>
       </c>
       <c r="E67">
-        <v>5.8995</v>
+        <v>5.9978</v>
       </c>
       <c r="F67">
-        <v>6.3895</v>
+        <v>6.4878</v>
       </c>
       <c r="G67">
         <v>2.29</v>
@@ -6781,28 +6781,28 @@
         <v>1.123</v>
       </c>
       <c r="M67">
-        <v>0.4843241</v>
+        <v>0.4917752400000001</v>
       </c>
       <c r="N67">
-        <v>0.6386759</v>
+        <v>0.6312247599999999</v>
       </c>
       <c r="O67">
-        <v>0.159668975</v>
+        <v>0.15780619</v>
       </c>
       <c r="P67">
-        <v>0.479006925</v>
+        <v>0.47341857</v>
       </c>
       <c r="Q67">
-        <v>0.8160069249999999</v>
+        <v>0.8104185699999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1984584492640041</v>
+        <v>0.2024793039417215</v>
       </c>
       <c r="T67">
-        <v>1.476323878548164</v>
+        <v>1.515208616350135</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.318695270377832</v>
+        <v>2.283563523856955</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1063639633401853</v>
+        <v>0.1063149694379692</v>
       </c>
       <c r="C68">
-        <v>3.560058204736091</v>
+        <v>3.464516303806645</v>
       </c>
       <c r="D68">
-        <v>7.757858204736091</v>
+        <v>7.760616303806646</v>
       </c>
       <c r="E68">
-        <v>5.9978</v>
+        <v>6.0961</v>
       </c>
       <c r="F68">
-        <v>6.4878</v>
+        <v>6.5861</v>
       </c>
       <c r="G68">
         <v>2.29</v>
@@ -6863,28 +6863,28 @@
         <v>1.123</v>
       </c>
       <c r="M68">
-        <v>0.4917752400000001</v>
+        <v>0.49922638</v>
       </c>
       <c r="N68">
-        <v>0.6312247599999999</v>
+        <v>0.6237736199999999</v>
       </c>
       <c r="O68">
-        <v>0.15780619</v>
+        <v>0.155943405</v>
       </c>
       <c r="P68">
-        <v>0.47341857</v>
+        <v>0.4678302149999999</v>
       </c>
       <c r="Q68">
-        <v>0.8104185699999999</v>
+        <v>0.804830215</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2024793039417215</v>
+        <v>0.2067438467817247</v>
       </c>
       <c r="T68">
-        <v>1.515208616350135</v>
+        <v>1.556450004927983</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.283563523856955</v>
+        <v>2.249480486187449</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1063149694379692</v>
+        <v>0.1062659755357531</v>
       </c>
       <c r="C69">
-        <v>3.464516303806645</v>
+        <v>3.368976364711447</v>
       </c>
       <c r="D69">
-        <v>7.760616303806646</v>
+        <v>7.763376364711446</v>
       </c>
       <c r="E69">
-        <v>6.0961</v>
+        <v>6.1944</v>
       </c>
       <c r="F69">
-        <v>6.5861</v>
+        <v>6.6844</v>
       </c>
       <c r="G69">
         <v>2.29</v>
@@ -6945,28 +6945,28 @@
         <v>1.123</v>
       </c>
       <c r="M69">
-        <v>0.49922638</v>
+        <v>0.5066775200000001</v>
       </c>
       <c r="N69">
-        <v>0.6237736199999999</v>
+        <v>0.6163224799999999</v>
       </c>
       <c r="O69">
-        <v>0.155943405</v>
+        <v>0.15408062</v>
       </c>
       <c r="P69">
-        <v>0.4678302149999999</v>
+        <v>0.4622418599999999</v>
       </c>
       <c r="Q69">
-        <v>0.804830215</v>
+        <v>0.79924186</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2067438467817247</v>
+        <v>0.2112749235492283</v>
       </c>
       <c r="T69">
-        <v>1.556450004927983</v>
+        <v>1.600268980291947</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.249480486187449</v>
+        <v>2.216399890802339</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1062659755357531</v>
+        <v>0.1062169816335369</v>
       </c>
       <c r="C70">
-        <v>3.368976364711447</v>
+        <v>3.273438389544413</v>
       </c>
       <c r="D70">
-        <v>7.763376364711446</v>
+        <v>7.766138389544413</v>
       </c>
       <c r="E70">
-        <v>6.1944</v>
+        <v>6.2927</v>
       </c>
       <c r="F70">
-        <v>6.6844</v>
+        <v>6.7827</v>
       </c>
       <c r="G70">
         <v>2.29</v>
@@ -7027,28 +7027,28 @@
         <v>1.123</v>
       </c>
       <c r="M70">
-        <v>0.5066775200000001</v>
+        <v>0.51412866</v>
       </c>
       <c r="N70">
-        <v>0.6163224799999999</v>
+        <v>0.60887134</v>
       </c>
       <c r="O70">
-        <v>0.15408062</v>
+        <v>0.152217835</v>
       </c>
       <c r="P70">
-        <v>0.4622418599999999</v>
+        <v>0.456653505</v>
       </c>
       <c r="Q70">
-        <v>0.79924186</v>
+        <v>0.793653505</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2112749235492283</v>
+        <v>0.2160983278501191</v>
       </c>
       <c r="T70">
-        <v>1.600268980291947</v>
+        <v>1.646914986324553</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.216399890802339</v>
+        <v>2.184278153254479</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1062169816335369</v>
+        <v>0.1061679877313208</v>
       </c>
       <c r="C71">
-        <v>3.273438389544413</v>
+        <v>3.177902380402453</v>
       </c>
       <c r="D71">
-        <v>7.766138389544413</v>
+        <v>7.768902380402453</v>
       </c>
       <c r="E71">
-        <v>6.2927</v>
+        <v>6.391000000000001</v>
       </c>
       <c r="F71">
-        <v>6.7827</v>
+        <v>6.881000000000001</v>
       </c>
       <c r="G71">
         <v>2.29</v>
@@ -7109,28 +7109,28 @@
         <v>1.123</v>
       </c>
       <c r="M71">
-        <v>0.51412866</v>
+        <v>0.5215798000000001</v>
       </c>
       <c r="N71">
-        <v>0.60887134</v>
+        <v>0.6014201999999998</v>
       </c>
       <c r="O71">
-        <v>0.152217835</v>
+        <v>0.15035505</v>
       </c>
       <c r="P71">
-        <v>0.456653505</v>
+        <v>0.4510651499999999</v>
       </c>
       <c r="Q71">
-        <v>0.793653505</v>
+        <v>0.78806515</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2160983278501191</v>
+        <v>0.221243292437736</v>
       </c>
       <c r="T71">
-        <v>1.646914986324553</v>
+        <v>1.696670726092667</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.184278153254479</v>
+        <v>2.153074179636557</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1061679877313208</v>
+        <v>0.1061189938291047</v>
       </c>
       <c r="C72">
-        <v>3.177902380402453</v>
+        <v>3.082368339385451</v>
       </c>
       <c r="D72">
-        <v>7.768902380402453</v>
+        <v>7.771668339385452</v>
       </c>
       <c r="E72">
-        <v>6.391000000000001</v>
+        <v>6.489300000000001</v>
       </c>
       <c r="F72">
-        <v>6.881000000000001</v>
+        <v>6.979300000000001</v>
       </c>
       <c r="G72">
         <v>2.29</v>
@@ -7191,28 +7191,28 @@
         <v>1.123</v>
       </c>
       <c r="M72">
-        <v>0.5215798000000001</v>
+        <v>0.5290309400000002</v>
       </c>
       <c r="N72">
-        <v>0.6014201999999998</v>
+        <v>0.5939690599999998</v>
       </c>
       <c r="O72">
-        <v>0.15035505</v>
+        <v>0.148492265</v>
       </c>
       <c r="P72">
-        <v>0.4510651499999999</v>
+        <v>0.4454767949999999</v>
       </c>
       <c r="Q72">
-        <v>0.78806515</v>
+        <v>0.7824767949999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.221243292437736</v>
+        <v>0.2267430821693265</v>
       </c>
       <c r="T72">
-        <v>1.696670726092667</v>
+        <v>1.749857896189616</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.153074179636557</v>
+        <v>2.122749191190972</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1061189938291047</v>
+        <v>0.1060699999268886</v>
       </c>
       <c r="C73">
-        <v>3.082368339385453</v>
+        <v>2.986836268596293</v>
       </c>
       <c r="D73">
-        <v>7.771668339385452</v>
+        <v>7.774436268596292</v>
       </c>
       <c r="E73">
-        <v>6.489299999999999</v>
+        <v>6.587599999999999</v>
       </c>
       <c r="F73">
-        <v>6.979299999999999</v>
+        <v>7.077599999999999</v>
       </c>
       <c r="G73">
         <v>2.29</v>
@@ -7273,28 +7273,28 @@
         <v>1.123</v>
       </c>
       <c r="M73">
-        <v>0.5290309399999999</v>
+        <v>0.53648208</v>
       </c>
       <c r="N73">
-        <v>0.59396906</v>
+        <v>0.58651792</v>
       </c>
       <c r="O73">
-        <v>0.148492265</v>
+        <v>0.14662948</v>
       </c>
       <c r="P73">
-        <v>0.445476795</v>
+        <v>0.43988844</v>
       </c>
       <c r="Q73">
-        <v>0.782476795</v>
+        <v>0.77688844</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2267430821693265</v>
+        <v>0.232635714024602</v>
       </c>
       <c r="T73">
-        <v>1.749857896189615</v>
+        <v>1.806844149864917</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.122749191190973</v>
+        <v>2.093266563535543</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1060699999268886</v>
+        <v>0.1060210060246724</v>
       </c>
       <c r="C74">
-        <v>2.986836268596293</v>
+        <v>2.89130617014085</v>
       </c>
       <c r="D74">
-        <v>7.774436268596292</v>
+        <v>7.777206170140849</v>
       </c>
       <c r="E74">
-        <v>6.587599999999999</v>
+        <v>6.685899999999999</v>
       </c>
       <c r="F74">
-        <v>7.077599999999999</v>
+        <v>7.1759</v>
       </c>
       <c r="G74">
         <v>2.29</v>
@@ -7355,28 +7355,28 @@
         <v>1.123</v>
       </c>
       <c r="M74">
-        <v>0.53648208</v>
+        <v>0.54393322</v>
       </c>
       <c r="N74">
-        <v>0.58651792</v>
+        <v>0.57906678</v>
       </c>
       <c r="O74">
-        <v>0.14662948</v>
+        <v>0.144766695</v>
       </c>
       <c r="P74">
-        <v>0.43988844</v>
+        <v>0.434300085</v>
       </c>
       <c r="Q74">
-        <v>0.77688844</v>
+        <v>0.771300085</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.232635714024602</v>
+        <v>0.2389648371284164</v>
       </c>
       <c r="T74">
-        <v>1.806844149864917</v>
+        <v>1.868051607516168</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.093266563535543</v>
+        <v>2.064591679103549</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1060210060246724</v>
+        <v>0.1059720121224563</v>
       </c>
       <c r="C75">
-        <v>2.89130617014085</v>
+        <v>2.795778046128004</v>
       </c>
       <c r="D75">
-        <v>7.777206170140849</v>
+        <v>7.779978046128004</v>
       </c>
       <c r="E75">
-        <v>6.685899999999999</v>
+        <v>6.784199999999999</v>
       </c>
       <c r="F75">
-        <v>7.1759</v>
+        <v>7.2742</v>
       </c>
       <c r="G75">
         <v>2.29</v>
@@ -7437,28 +7437,28 @@
         <v>1.123</v>
       </c>
       <c r="M75">
-        <v>0.54393322</v>
+        <v>0.55138436</v>
       </c>
       <c r="N75">
-        <v>0.57906678</v>
+        <v>0.57161564</v>
       </c>
       <c r="O75">
-        <v>0.144766695</v>
+        <v>0.14290391</v>
       </c>
       <c r="P75">
-        <v>0.434300085</v>
+        <v>0.42871173</v>
       </c>
       <c r="Q75">
-        <v>0.771300085</v>
+        <v>0.76571173</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2389648371284164</v>
+        <v>0.2457808158556011</v>
       </c>
       <c r="T75">
-        <v>1.868051607516168</v>
+        <v>1.933967331140591</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.064591679103549</v>
+        <v>2.036691791548095</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1059720121224563</v>
+        <v>0.1059230182202402</v>
       </c>
       <c r="C76">
-        <v>2.795778046128004</v>
+        <v>2.700251898669647</v>
       </c>
       <c r="D76">
-        <v>7.779978046128004</v>
+        <v>7.782751898669646</v>
       </c>
       <c r="E76">
-        <v>6.784199999999999</v>
+        <v>6.8825</v>
       </c>
       <c r="F76">
-        <v>7.2742</v>
+        <v>7.3725</v>
       </c>
       <c r="G76">
         <v>2.29</v>
@@ -7519,28 +7519,28 @@
         <v>1.123</v>
       </c>
       <c r="M76">
-        <v>0.55138436</v>
+        <v>0.5588355</v>
       </c>
       <c r="N76">
-        <v>0.57161564</v>
+        <v>0.5641645</v>
       </c>
       <c r="O76">
-        <v>0.14290391</v>
+        <v>0.141041125</v>
       </c>
       <c r="P76">
-        <v>0.42871173</v>
+        <v>0.423123375</v>
       </c>
       <c r="Q76">
-        <v>0.76571173</v>
+        <v>0.760123375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2457808158556011</v>
+        <v>0.2531420728809607</v>
       </c>
       <c r="T76">
-        <v>1.933967331140591</v>
+        <v>2.005156312654969</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.036691791548095</v>
+        <v>2.009535900994121</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1059230182202402</v>
+        <v>0.1139680243180241</v>
       </c>
       <c r="C77">
-        <v>2.700251898669647</v>
+        <v>2.171511294865715</v>
       </c>
       <c r="D77">
-        <v>7.782751898669646</v>
+        <v>7.352311294865715</v>
       </c>
       <c r="E77">
-        <v>6.8825</v>
+        <v>6.9808</v>
       </c>
       <c r="F77">
-        <v>7.3725</v>
+        <v>7.470800000000001</v>
       </c>
       <c r="G77">
         <v>2.29</v>
@@ -7601,45 +7601,45 @@
         <v>1.123</v>
       </c>
       <c r="M77">
-        <v>0.5588355</v>
+        <v>0.672372</v>
       </c>
       <c r="N77">
-        <v>0.5641645</v>
+        <v>0.450628</v>
       </c>
       <c r="O77">
-        <v>0.141041125</v>
+        <v>0.112657</v>
       </c>
       <c r="P77">
-        <v>0.423123375</v>
+        <v>0.337971</v>
       </c>
       <c r="Q77">
-        <v>0.760123375</v>
+        <v>0.674971</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2531420728809607</v>
+        <v>0.2611167679917669</v>
       </c>
       <c r="T77">
-        <v>2.005156312654969</v>
+        <v>2.082277709295545</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.009535900994121</v>
+        <v>1.67020637385257</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1139680243180241</v>
+        <v>0.1140255304158079</v>
       </c>
       <c r="C78">
-        <v>2.171511294865715</v>
+        <v>2.070305802125542</v>
       </c>
       <c r="D78">
-        <v>7.352311294865715</v>
+        <v>7.349405802125543</v>
       </c>
       <c r="E78">
-        <v>6.9808</v>
+        <v>7.0791</v>
       </c>
       <c r="F78">
-        <v>7.470800000000001</v>
+        <v>7.569100000000001</v>
       </c>
       <c r="G78">
         <v>2.29</v>
@@ -7683,28 +7683,28 @@
         <v>1.123</v>
       </c>
       <c r="M78">
-        <v>0.672372</v>
+        <v>0.681219</v>
       </c>
       <c r="N78">
-        <v>0.450628</v>
+        <v>0.441781</v>
       </c>
       <c r="O78">
-        <v>0.112657</v>
+        <v>0.11044525</v>
       </c>
       <c r="P78">
-        <v>0.337971</v>
+        <v>0.33133575</v>
       </c>
       <c r="Q78">
-        <v>0.674971</v>
+        <v>0.66833575</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2611167679917669</v>
+        <v>0.2697849148513388</v>
       </c>
       <c r="T78">
-        <v>2.082277709295545</v>
+        <v>2.166105314339649</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.67020637385257</v>
+        <v>1.648515381984355</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1140255304158079</v>
+        <v>0.1140830365135918</v>
       </c>
       <c r="C79">
-        <v>2.070305802125542</v>
+        <v>1.96910260486851</v>
       </c>
       <c r="D79">
-        <v>7.349405802125543</v>
+        <v>7.346502604868512</v>
       </c>
       <c r="E79">
-        <v>7.0791</v>
+        <v>7.1774</v>
       </c>
       <c r="F79">
-        <v>7.569100000000001</v>
+        <v>7.667400000000001</v>
       </c>
       <c r="G79">
         <v>2.29</v>
@@ -7765,28 +7765,28 @@
         <v>1.123</v>
       </c>
       <c r="M79">
-        <v>0.681219</v>
+        <v>0.6900660000000001</v>
       </c>
       <c r="N79">
-        <v>0.441781</v>
+        <v>0.4329339999999999</v>
       </c>
       <c r="O79">
-        <v>0.11044525</v>
+        <v>0.1082335</v>
       </c>
       <c r="P79">
-        <v>0.33133575</v>
+        <v>0.3247004999999999</v>
       </c>
       <c r="Q79">
-        <v>0.66833575</v>
+        <v>0.6617005</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2697849148513388</v>
+        <v>0.2792410750617809</v>
       </c>
       <c r="T79">
-        <v>2.166105314339649</v>
+        <v>2.257553610751399</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.648515381984355</v>
+        <v>1.627380569394811</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1140830365135918</v>
+        <v>0.1141405426113757</v>
       </c>
       <c r="C80">
-        <v>1.96910260486851</v>
+        <v>1.867901700375375</v>
       </c>
       <c r="D80">
-        <v>7.346502604868512</v>
+        <v>7.343601700375375</v>
       </c>
       <c r="E80">
-        <v>7.1774</v>
+        <v>7.275700000000001</v>
       </c>
       <c r="F80">
-        <v>7.667400000000001</v>
+        <v>7.765700000000001</v>
       </c>
       <c r="G80">
         <v>2.29</v>
@@ -7847,28 +7847,28 @@
         <v>1.123</v>
       </c>
       <c r="M80">
-        <v>0.6900660000000001</v>
+        <v>0.698913</v>
       </c>
       <c r="N80">
-        <v>0.4329339999999999</v>
+        <v>0.424087</v>
       </c>
       <c r="O80">
-        <v>0.1082335</v>
+        <v>0.10602175</v>
       </c>
       <c r="P80">
-        <v>0.3247004999999999</v>
+        <v>0.31806525</v>
       </c>
       <c r="Q80">
-        <v>0.6617005</v>
+        <v>0.65506525</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2792410750617809</v>
+        <v>0.2895978219589319</v>
       </c>
       <c r="T80">
-        <v>2.257553610751399</v>
+        <v>2.357711268726173</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.627380569394811</v>
+        <v>1.606780815351839</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1141405426113757</v>
+        <v>0.1141980487091596</v>
       </c>
       <c r="C81">
-        <v>1.867901700375375</v>
+        <v>1.766703085931184</v>
       </c>
       <c r="D81">
-        <v>7.343601700375375</v>
+        <v>7.340703085931185</v>
       </c>
       <c r="E81">
-        <v>7.275700000000001</v>
+        <v>7.374000000000001</v>
       </c>
       <c r="F81">
-        <v>7.765700000000001</v>
+        <v>7.864000000000001</v>
       </c>
       <c r="G81">
         <v>2.29</v>
@@ -7929,28 +7929,28 @@
         <v>1.123</v>
       </c>
       <c r="M81">
-        <v>0.698913</v>
+        <v>0.7077600000000001</v>
       </c>
       <c r="N81">
-        <v>0.424087</v>
+        <v>0.4152399999999999</v>
       </c>
       <c r="O81">
-        <v>0.10602175</v>
+        <v>0.10381</v>
       </c>
       <c r="P81">
-        <v>0.31806525</v>
+        <v>0.31143</v>
       </c>
       <c r="Q81">
-        <v>0.65506525</v>
+        <v>0.6484300000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2895978219589319</v>
+        <v>0.3009902435457978</v>
       </c>
       <c r="T81">
-        <v>2.357711268726173</v>
+        <v>2.467884692498424</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.606780815351839</v>
+        <v>1.586696055159941</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1141980487091596</v>
+        <v>0.1142555548069434</v>
       </c>
       <c r="C82">
-        <v>1.766703085931184</v>
+        <v>1.665506758825275</v>
       </c>
       <c r="D82">
-        <v>7.340703085931185</v>
+        <v>7.337806758825275</v>
       </c>
       <c r="E82">
-        <v>7.374000000000001</v>
+        <v>7.472300000000001</v>
       </c>
       <c r="F82">
-        <v>7.864000000000001</v>
+        <v>7.962300000000001</v>
       </c>
       <c r="G82">
         <v>2.29</v>
@@ -8011,28 +8011,28 @@
         <v>1.123</v>
       </c>
       <c r="M82">
-        <v>0.7077600000000001</v>
+        <v>0.716607</v>
       </c>
       <c r="N82">
-        <v>0.4152399999999999</v>
+        <v>0.406393</v>
       </c>
       <c r="O82">
-        <v>0.10381</v>
+        <v>0.10159825</v>
       </c>
       <c r="P82">
-        <v>0.31143</v>
+        <v>0.30479475</v>
       </c>
       <c r="Q82">
-        <v>0.6484300000000001</v>
+        <v>0.6417947500000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3009902435457978</v>
+        <v>0.3135818674049655</v>
       </c>
       <c r="T82">
-        <v>2.467884692498424</v>
+        <v>2.589655318773018</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.586696055159941</v>
+        <v>1.567107214972781</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1142555548069434</v>
+        <v>0.1143130609047273</v>
       </c>
       <c r="C83">
-        <v>1.665506758825275</v>
+        <v>1.564312716351253</v>
       </c>
       <c r="D83">
-        <v>7.337806758825275</v>
+        <v>7.334912716351254</v>
       </c>
       <c r="E83">
-        <v>7.472300000000001</v>
+        <v>7.570600000000001</v>
       </c>
       <c r="F83">
-        <v>7.962300000000001</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="G83">
         <v>2.29</v>
@@ -8093,28 +8093,28 @@
         <v>1.123</v>
       </c>
       <c r="M83">
-        <v>0.716607</v>
+        <v>0.725454</v>
       </c>
       <c r="N83">
-        <v>0.406393</v>
+        <v>0.397546</v>
       </c>
       <c r="O83">
-        <v>0.10159825</v>
+        <v>0.09938649999999999</v>
       </c>
       <c r="P83">
-        <v>0.30479475</v>
+        <v>0.2981595</v>
       </c>
       <c r="Q83">
-        <v>0.6417947500000001</v>
+        <v>0.6351595</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3135818674049655</v>
+        <v>0.3275725605818185</v>
       </c>
       <c r="T83">
-        <v>2.589655318773018</v>
+        <v>2.724956014633677</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.567107214972781</v>
+        <v>1.547996151375552</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1143130609047273</v>
+        <v>0.1143705670025112</v>
       </c>
       <c r="C84">
-        <v>1.564312716351253</v>
+        <v>1.463120955807002</v>
       </c>
       <c r="D84">
-        <v>7.334912716351254</v>
+        <v>7.332020955807003</v>
       </c>
       <c r="E84">
-        <v>7.570600000000001</v>
+        <v>7.668900000000001</v>
       </c>
       <c r="F84">
-        <v>8.060600000000001</v>
+        <v>8.158900000000001</v>
       </c>
       <c r="G84">
         <v>2.29</v>
@@ -8175,28 +8175,28 @@
         <v>1.123</v>
       </c>
       <c r="M84">
-        <v>0.725454</v>
+        <v>0.7343010000000001</v>
       </c>
       <c r="N84">
-        <v>0.397546</v>
+        <v>0.3886989999999999</v>
       </c>
       <c r="O84">
-        <v>0.09938649999999999</v>
+        <v>0.09717474999999998</v>
       </c>
       <c r="P84">
-        <v>0.2981595</v>
+        <v>0.2915242499999999</v>
       </c>
       <c r="Q84">
-        <v>0.6351595</v>
+        <v>0.6285242499999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3275725605818185</v>
+        <v>0.3432092176618307</v>
       </c>
       <c r="T84">
-        <v>2.724956014633677</v>
+        <v>2.87617443941912</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.547996151375552</v>
+        <v>1.529345595334883</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1143705670025112</v>
+        <v>0.1144280731002951</v>
       </c>
       <c r="C85">
-        <v>1.463120955807002</v>
+        <v>1.361931474494657</v>
       </c>
       <c r="D85">
-        <v>7.332020955807003</v>
+        <v>7.329131474494659</v>
       </c>
       <c r="E85">
-        <v>7.668900000000001</v>
+        <v>7.767200000000001</v>
       </c>
       <c r="F85">
-        <v>8.158900000000001</v>
+        <v>8.257200000000001</v>
       </c>
       <c r="G85">
         <v>2.29</v>
@@ -8257,28 +8257,28 @@
         <v>1.123</v>
       </c>
       <c r="M85">
-        <v>0.7343010000000001</v>
+        <v>0.743148</v>
       </c>
       <c r="N85">
-        <v>0.3886989999999999</v>
+        <v>0.379852</v>
       </c>
       <c r="O85">
-        <v>0.09717474999999998</v>
+        <v>0.09496299999999999</v>
       </c>
       <c r="P85">
-        <v>0.2915242499999999</v>
+        <v>0.2848889999999999</v>
       </c>
       <c r="Q85">
-        <v>0.6285242499999999</v>
+        <v>0.6218889999999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3432092176618307</v>
+        <v>0.3608004568768443</v>
       </c>
       <c r="T85">
-        <v>2.87617443941912</v>
+        <v>3.046295167302743</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.529345595334883</v>
+        <v>1.511139100152325</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1144280731002951</v>
+        <v>0.154474960453704</v>
       </c>
       <c r="C86">
-        <v>1.361931474494659</v>
+        <v>-0.3146461254534927</v>
       </c>
       <c r="D86">
-        <v>7.329131474494659</v>
+        <v>5.750853874546507</v>
       </c>
       <c r="E86">
-        <v>7.767199999999999</v>
+        <v>7.865499999999999</v>
       </c>
       <c r="F86">
-        <v>8.257199999999999</v>
+        <v>8.355499999999999</v>
       </c>
       <c r="G86">
         <v>2.29</v>
@@ -8339,45 +8339,45 @@
         <v>1.123</v>
       </c>
       <c r="M86">
-        <v>0.7431479999999999</v>
+        <v>1.2265874</v>
       </c>
       <c r="N86">
-        <v>0.3798520000000001</v>
+        <v>-0.1035874000000001</v>
       </c>
       <c r="O86">
-        <v>0.09496300000000002</v>
+        <v>-0.02589685000000003</v>
       </c>
       <c r="P86">
-        <v>0.2848890000000001</v>
+        <v>-0.07769055000000008</v>
       </c>
       <c r="Q86">
-        <v>0.6218890000000001</v>
+        <v>0.2593094499999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3608004568768441</v>
+        <v>0.3883699296438864</v>
       </c>
       <c r="T86">
-        <v>3.046295167302741</v>
+        <v>3.312913039822721</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.25</v>
+        <v>0.2288870731918492</v>
       </c>
       <c r="W86">
-        <v>0.0675</v>
+        <v>0.1131993776554365</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.511139100152325</v>
+        <v>0.9155482927673967</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.154474960453704</v>
+        <v>0.155484960453704</v>
       </c>
       <c r="C87">
-        <v>-0.3146461254534927</v>
+        <v>-0.4440105654650601</v>
       </c>
       <c r="D87">
-        <v>5.750853874546507</v>
+        <v>5.719789434534939</v>
       </c>
       <c r="E87">
-        <v>7.865499999999999</v>
+        <v>7.963799999999999</v>
       </c>
       <c r="F87">
-        <v>8.355499999999999</v>
+        <v>8.453799999999999</v>
       </c>
       <c r="G87">
         <v>2.29</v>
@@ -8421,37 +8421,37 @@
         <v>1.123</v>
       </c>
       <c r="M87">
-        <v>1.2265874</v>
+        <v>1.24101784</v>
       </c>
       <c r="N87">
-        <v>-0.1035874000000001</v>
+        <v>-0.11801784</v>
       </c>
       <c r="O87">
-        <v>-0.02589685000000003</v>
+        <v>-0.02950446000000001</v>
       </c>
       <c r="P87">
-        <v>-0.07769055000000008</v>
+        <v>-0.08851338000000003</v>
       </c>
       <c r="Q87">
-        <v>0.2593094499999999</v>
+        <v>0.24848662</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3883699296438864</v>
+        <v>0.4128392103327354</v>
       </c>
       <c r="T87">
-        <v>3.312913039822721</v>
+        <v>3.549549685524343</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2288870731918492</v>
+        <v>0.2262255955965951</v>
       </c>
       <c r="W87">
-        <v>0.1131993776554365</v>
+        <v>0.1135900825664198</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9155482927673967</v>
+        <v>0.9049023823863804</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.155484960453704</v>
+        <v>0.156494960453704</v>
       </c>
       <c r="C88">
-        <v>-0.4440105654650601</v>
+        <v>-0.5730412064221522</v>
       </c>
       <c r="D88">
-        <v>5.719789434534939</v>
+        <v>5.689058793577847</v>
       </c>
       <c r="E88">
-        <v>7.963799999999999</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="F88">
-        <v>8.453799999999999</v>
+        <v>8.552099999999999</v>
       </c>
       <c r="G88">
         <v>2.29</v>
@@ -8503,37 +8503,37 @@
         <v>1.123</v>
       </c>
       <c r="M88">
-        <v>1.24101784</v>
+        <v>1.25544828</v>
       </c>
       <c r="N88">
-        <v>-0.11801784</v>
+        <v>-0.13244828</v>
       </c>
       <c r="O88">
-        <v>-0.02950446000000001</v>
+        <v>-0.03311206999999999</v>
       </c>
       <c r="P88">
-        <v>-0.08851338000000003</v>
+        <v>-0.09933620999999998</v>
       </c>
       <c r="Q88">
-        <v>0.24848662</v>
+        <v>0.23766379</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4128392103327354</v>
+        <v>0.4410729957429459</v>
       </c>
       <c r="T88">
-        <v>3.549549685524343</v>
+        <v>3.822591969026216</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2262255955965951</v>
+        <v>0.2236253013943354</v>
       </c>
       <c r="W88">
-        <v>0.1135900825664198</v>
+        <v>0.1139718057553116</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9049023823863804</v>
+        <v>0.8945012055773417</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.156494960453704</v>
+        <v>0.157504960453704</v>
       </c>
       <c r="C89">
-        <v>-0.5730412064221522</v>
+        <v>-0.7017433997671194</v>
       </c>
       <c r="D89">
-        <v>5.689058793577847</v>
+        <v>5.65865660023288</v>
       </c>
       <c r="E89">
-        <v>8.062099999999999</v>
+        <v>8.160399999999999</v>
       </c>
       <c r="F89">
-        <v>8.552099999999999</v>
+        <v>8.650399999999999</v>
       </c>
       <c r="G89">
         <v>2.29</v>
@@ -8585,37 +8585,37 @@
         <v>1.123</v>
       </c>
       <c r="M89">
-        <v>1.25544828</v>
+        <v>1.26987872</v>
       </c>
       <c r="N89">
-        <v>-0.13244828</v>
+        <v>-0.1468787200000001</v>
       </c>
       <c r="O89">
-        <v>-0.03311206999999999</v>
+        <v>-0.03671968000000003</v>
       </c>
       <c r="P89">
-        <v>-0.09933620999999998</v>
+        <v>-0.1101590400000001</v>
       </c>
       <c r="Q89">
-        <v>0.23766379</v>
+        <v>0.2268409599999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4410729957429459</v>
+        <v>0.4740124120548581</v>
       </c>
       <c r="T89">
-        <v>3.822591969026216</v>
+        <v>4.141141299778401</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2236253013943354</v>
+        <v>0.2210841047875816</v>
       </c>
       <c r="W89">
-        <v>0.1139718057553116</v>
+        <v>0.114344853417183</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8945012055773417</v>
+        <v>0.8843364191503263</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.157504960453704</v>
+        <v>0.1585149604537041</v>
       </c>
       <c r="C90">
-        <v>-0.7017433997671194</v>
+        <v>-0.8301223831584572</v>
       </c>
       <c r="D90">
-        <v>5.65865660023288</v>
+        <v>5.628577616841542</v>
       </c>
       <c r="E90">
-        <v>8.160399999999999</v>
+        <v>8.258699999999999</v>
       </c>
       <c r="F90">
-        <v>8.650399999999999</v>
+        <v>8.748699999999999</v>
       </c>
       <c r="G90">
         <v>2.29</v>
@@ -8667,37 +8667,37 @@
         <v>1.123</v>
       </c>
       <c r="M90">
-        <v>1.26987872</v>
+        <v>1.28430916</v>
       </c>
       <c r="N90">
-        <v>-0.1468787200000001</v>
+        <v>-0.1613091600000001</v>
       </c>
       <c r="O90">
-        <v>-0.03671968000000003</v>
+        <v>-0.04032729000000002</v>
       </c>
       <c r="P90">
-        <v>-0.1101590400000001</v>
+        <v>-0.12098187</v>
       </c>
       <c r="Q90">
-        <v>0.2268409599999999</v>
+        <v>0.21601813</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4740124120548581</v>
+        <v>0.5129408131507543</v>
       </c>
       <c r="T90">
-        <v>4.141141299778401</v>
+        <v>4.517608690667347</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2210841047875816</v>
+        <v>0.2186000137225526</v>
       </c>
       <c r="W90">
-        <v>0.114344853417183</v>
+        <v>0.1147095179855293</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8843364191503263</v>
+        <v>0.8744000548902103</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1585149604537041</v>
+        <v>0.159524960453704</v>
       </c>
       <c r="C91">
-        <v>-0.8301223831584572</v>
+        <v>-0.9581832834789399</v>
       </c>
       <c r="D91">
-        <v>5.628577616841542</v>
+        <v>5.59881671652106</v>
       </c>
       <c r="E91">
-        <v>8.258699999999999</v>
+        <v>8.356999999999999</v>
       </c>
       <c r="F91">
-        <v>8.748699999999999</v>
+        <v>8.847</v>
       </c>
       <c r="G91">
         <v>2.29</v>
@@ -8749,37 +8749,37 @@
         <v>1.123</v>
       </c>
       <c r="M91">
-        <v>1.28430916</v>
+        <v>1.2987396</v>
       </c>
       <c r="N91">
-        <v>-0.1613091600000001</v>
+        <v>-0.1757396</v>
       </c>
       <c r="O91">
-        <v>-0.04032729000000002</v>
+        <v>-0.0439349</v>
       </c>
       <c r="P91">
-        <v>-0.12098187</v>
+        <v>-0.1318047</v>
       </c>
       <c r="Q91">
-        <v>0.21601813</v>
+        <v>0.2051953</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5129408131507543</v>
+        <v>0.5596548944658297</v>
       </c>
       <c r="T91">
-        <v>4.517608690667347</v>
+        <v>4.969369559734082</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2186000137225526</v>
+        <v>0.2161711246811909</v>
       </c>
       <c r="W91">
-        <v>0.1147095179855293</v>
+        <v>0.1150660788968012</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8744000548902103</v>
+        <v>0.8646844987247636</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.159524960453704</v>
+        <v>0.1605349604537041</v>
       </c>
       <c r="C92">
-        <v>-0.9581832834789399</v>
+        <v>-1.085931119748839</v>
       </c>
       <c r="D92">
-        <v>5.59881671652106</v>
+        <v>5.569368880251161</v>
       </c>
       <c r="E92">
-        <v>8.356999999999999</v>
+        <v>8.455299999999999</v>
       </c>
       <c r="F92">
-        <v>8.847</v>
+        <v>8.9453</v>
       </c>
       <c r="G92">
         <v>2.29</v>
@@ -8831,37 +8831,37 @@
         <v>1.123</v>
       </c>
       <c r="M92">
-        <v>1.2987396</v>
+        <v>1.31317004</v>
       </c>
       <c r="N92">
-        <v>-0.1757396</v>
+        <v>-0.1901700400000002</v>
       </c>
       <c r="O92">
-        <v>-0.0439349</v>
+        <v>-0.04754251000000004</v>
       </c>
       <c r="P92">
-        <v>-0.1318047</v>
+        <v>-0.1426275300000001</v>
       </c>
       <c r="Q92">
-        <v>0.2051953</v>
+        <v>0.1943724699999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5596548944658297</v>
+        <v>0.6167498827398109</v>
       </c>
       <c r="T92">
-        <v>4.969369559734082</v>
+        <v>5.521521733037869</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2161711246811909</v>
+        <v>0.2137956178165624</v>
       </c>
       <c r="W92">
-        <v>0.1150660788968012</v>
+        <v>0.1154148033045286</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8646844987247636</v>
+        <v>0.8551824712662497</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1605349604537041</v>
+        <v>0.161544960453704</v>
       </c>
       <c r="C93">
-        <v>-1.085931119748839</v>
+        <v>-1.213370805947664</v>
       </c>
       <c r="D93">
-        <v>5.569368880251161</v>
+        <v>5.540229194052335</v>
       </c>
       <c r="E93">
-        <v>8.455299999999999</v>
+        <v>8.553599999999999</v>
       </c>
       <c r="F93">
-        <v>8.9453</v>
+        <v>9.0436</v>
       </c>
       <c r="G93">
         <v>2.29</v>
@@ -8913,37 +8913,37 @@
         <v>1.123</v>
       </c>
       <c r="M93">
-        <v>1.31317004</v>
+        <v>1.32760048</v>
       </c>
       <c r="N93">
-        <v>-0.1901700400000002</v>
+        <v>-0.2046004800000001</v>
       </c>
       <c r="O93">
-        <v>-0.04754251000000004</v>
+        <v>-0.05115012000000002</v>
       </c>
       <c r="P93">
-        <v>-0.1426275300000001</v>
+        <v>-0.1534503600000001</v>
       </c>
       <c r="Q93">
-        <v>0.1943724699999999</v>
+        <v>0.18354964</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6167498827398109</v>
+        <v>0.6881186180822874</v>
       </c>
       <c r="T93">
-        <v>5.521521733037869</v>
+        <v>6.211711949667604</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2137956178165624</v>
+        <v>0.2114717524055128</v>
       </c>
       <c r="W93">
-        <v>0.1154148033045286</v>
+        <v>0.1157559467468707</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8551824712662497</v>
+        <v>0.8458870096220513</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.161544960453704</v>
+        <v>0.162554960453704</v>
       </c>
       <c r="C94">
-        <v>-1.213370805947664</v>
+        <v>-1.340507153747811</v>
       </c>
       <c r="D94">
-        <v>5.540229194052335</v>
+        <v>5.511392846252189</v>
       </c>
       <c r="E94">
-        <v>8.553599999999999</v>
+        <v>8.651899999999999</v>
       </c>
       <c r="F94">
-        <v>9.0436</v>
+        <v>9.1419</v>
       </c>
       <c r="G94">
         <v>2.29</v>
@@ -8995,37 +8995,37 @@
         <v>1.123</v>
       </c>
       <c r="M94">
-        <v>1.32760048</v>
+        <v>1.34203092</v>
       </c>
       <c r="N94">
-        <v>-0.2046004800000001</v>
+        <v>-0.21903092</v>
       </c>
       <c r="O94">
-        <v>-0.05115012000000002</v>
+        <v>-0.05475773</v>
       </c>
       <c r="P94">
-        <v>-0.1534503600000001</v>
+        <v>-0.16427319</v>
       </c>
       <c r="Q94">
-        <v>0.18354964</v>
+        <v>0.17272681</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6881186180822874</v>
+        <v>0.7798784206654714</v>
       </c>
       <c r="T94">
-        <v>6.211711949667604</v>
+        <v>7.099099371048692</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2114717524055128</v>
+        <v>0.2091978625947009</v>
       </c>
       <c r="W94">
-        <v>0.1157559467468707</v>
+        <v>0.1160897537710979</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8458870096220513</v>
+        <v>0.8367914503788034</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.162554960453704</v>
+        <v>0.1635649604537041</v>
       </c>
       <c r="C95">
-        <v>-1.340507153747811</v>
+        <v>-1.467344875163263</v>
       </c>
       <c r="D95">
-        <v>5.511392846252189</v>
+        <v>5.482855124836737</v>
       </c>
       <c r="E95">
-        <v>8.651899999999999</v>
+        <v>8.7502</v>
       </c>
       <c r="F95">
-        <v>9.1419</v>
+        <v>9.2402</v>
       </c>
       <c r="G95">
         <v>2.29</v>
@@ -9077,37 +9077,37 @@
         <v>1.123</v>
       </c>
       <c r="M95">
-        <v>1.34203092</v>
+        <v>1.35646136</v>
       </c>
       <c r="N95">
-        <v>-0.21903092</v>
+        <v>-0.2334613600000002</v>
       </c>
       <c r="O95">
-        <v>-0.05475773</v>
+        <v>-0.05836534000000004</v>
       </c>
       <c r="P95">
-        <v>-0.16427319</v>
+        <v>-0.1750960200000001</v>
       </c>
       <c r="Q95">
-        <v>0.17272681</v>
+        <v>0.1619039799999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7798784206654714</v>
+        <v>0.9022248241097169</v>
       </c>
       <c r="T95">
-        <v>7.099099371048692</v>
+        <v>8.28228259955681</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2091978625947009</v>
+        <v>0.2069723534181615</v>
       </c>
       <c r="W95">
-        <v>0.1160897537710979</v>
+        <v>0.1164164585182139</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8367914503788034</v>
+        <v>0.8278894136726459</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1635649604537041</v>
+        <v>0.1645749604537041</v>
       </c>
       <c r="C96">
-        <v>-1.467344875163263</v>
+        <v>-1.593888585116427</v>
       </c>
       <c r="D96">
-        <v>5.482855124836737</v>
+        <v>5.454611414883574</v>
       </c>
       <c r="E96">
-        <v>8.7502</v>
+        <v>8.848500000000001</v>
       </c>
       <c r="F96">
-        <v>9.2402</v>
+        <v>9.338500000000002</v>
       </c>
       <c r="G96">
         <v>2.29</v>
@@ -9159,37 +9159,37 @@
         <v>1.123</v>
       </c>
       <c r="M96">
-        <v>1.35646136</v>
+        <v>1.3708918</v>
       </c>
       <c r="N96">
-        <v>-0.2334613600000002</v>
+        <v>-0.2478918000000003</v>
       </c>
       <c r="O96">
-        <v>-0.05836534000000004</v>
+        <v>-0.06197295000000008</v>
       </c>
       <c r="P96">
-        <v>-0.1750960200000001</v>
+        <v>-0.1859188500000002</v>
       </c>
       <c r="Q96">
-        <v>0.1619039799999999</v>
+        <v>0.1510811499999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9022248241097169</v>
+        <v>1.073509788931661</v>
       </c>
       <c r="T96">
-        <v>8.28228259955681</v>
+        <v>9.938739119468178</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2069723534181615</v>
+        <v>0.2047936970663913</v>
       </c>
       <c r="W96">
-        <v>0.1164164585182139</v>
+        <v>0.1167362852706538</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8278894136726459</v>
+        <v>0.8191747882655653</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1645749604537041</v>
+        <v>0.165584960453704</v>
       </c>
       <c r="C97">
-        <v>-1.593888585116427</v>
+        <v>-1.720142803926052</v>
       </c>
       <c r="D97">
-        <v>5.454611414883574</v>
+        <v>5.42665719607395</v>
       </c>
       <c r="E97">
-        <v>8.848500000000001</v>
+        <v>8.946800000000001</v>
       </c>
       <c r="F97">
-        <v>9.338500000000002</v>
+        <v>9.436800000000002</v>
       </c>
       <c r="G97">
         <v>2.29</v>
@@ -9241,37 +9241,37 @@
         <v>1.123</v>
       </c>
       <c r="M97">
-        <v>1.3708918</v>
+        <v>1.38532224</v>
       </c>
       <c r="N97">
-        <v>-0.2478918000000003</v>
+        <v>-0.2623222400000003</v>
       </c>
       <c r="O97">
-        <v>-0.06197295000000008</v>
+        <v>-0.06558056000000007</v>
       </c>
       <c r="P97">
-        <v>-0.1859188500000002</v>
+        <v>-0.1967416800000002</v>
       </c>
       <c r="Q97">
-        <v>0.1510811499999998</v>
+        <v>0.1402583199999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.073509788931661</v>
+        <v>1.330437236164577</v>
       </c>
       <c r="T97">
-        <v>9.938739119468178</v>
+        <v>12.42342389933523</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2047936970663913</v>
+        <v>0.2026604293886164</v>
       </c>
       <c r="W97">
-        <v>0.1167362852706538</v>
+        <v>0.1170494489657511</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8191747882655653</v>
+        <v>0.8106417175544658</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.165584960453704</v>
+        <v>0.1665949604537041</v>
       </c>
       <c r="C98">
-        <v>-1.720142803926049</v>
+        <v>-1.846111959719027</v>
       </c>
       <c r="D98">
-        <v>5.42665719607395</v>
+        <v>5.398988040280972</v>
       </c>
       <c r="E98">
-        <v>8.9468</v>
+        <v>9.0451</v>
       </c>
       <c r="F98">
-        <v>9.4368</v>
+        <v>9.5351</v>
       </c>
       <c r="G98">
         <v>2.29</v>
@@ -9323,37 +9323,37 @@
         <v>1.123</v>
       </c>
       <c r="M98">
-        <v>1.38532224</v>
+        <v>1.39975268</v>
       </c>
       <c r="N98">
-        <v>-0.26232224</v>
+        <v>-0.2767526800000002</v>
       </c>
       <c r="O98">
-        <v>-0.06558056000000001</v>
+        <v>-0.06918817000000005</v>
       </c>
       <c r="P98">
-        <v>-0.19674168</v>
+        <v>-0.2075645100000001</v>
       </c>
       <c r="Q98">
-        <v>0.14025832</v>
+        <v>0.1294354899999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.330437236164573</v>
+        <v>1.758649648219431</v>
       </c>
       <c r="T98">
-        <v>12.42342389933519</v>
+        <v>16.56456519911359</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2026604293886165</v>
+        <v>0.2005711466114142</v>
       </c>
       <c r="W98">
-        <v>0.1170494489657511</v>
+        <v>0.1173561556774444</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8106417175544659</v>
+        <v>0.8022845864456568</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1665949604537041</v>
+        <v>0.2238628681118355</v>
       </c>
       <c r="C99">
-        <v>-1.846111959719027</v>
+        <v>-3.155227581218608</v>
       </c>
       <c r="D99">
-        <v>5.398988040280972</v>
+        <v>4.188172418781392</v>
       </c>
       <c r="E99">
-        <v>9.0451</v>
+        <v>9.1434</v>
       </c>
       <c r="F99">
-        <v>9.5351</v>
+        <v>9.6334</v>
       </c>
       <c r="G99">
         <v>2.29</v>
@@ -9405,45 +9405,45 @@
         <v>1.123</v>
       </c>
       <c r="M99">
-        <v>1.39975268</v>
+        <v>1.93438672</v>
       </c>
       <c r="N99">
-        <v>-0.2767526800000002</v>
+        <v>-0.81138672</v>
       </c>
       <c r="O99">
-        <v>-0.06918817000000005</v>
+        <v>-0.20284668</v>
       </c>
       <c r="P99">
-        <v>-0.2075645100000001</v>
+        <v>-0.6085400400000001</v>
       </c>
       <c r="Q99">
-        <v>0.1294354899999999</v>
+        <v>-0.27154004</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.758649648219431</v>
+        <v>2.781969855235717</v>
       </c>
       <c r="T99">
-        <v>16.56456519911359</v>
+        <v>26.46085370657992</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.2005711466114142</v>
+        <v>0.1451364389019379</v>
       </c>
       <c r="W99">
-        <v>0.1173561556774444</v>
+        <v>0.1716566030684909</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8022845864456568</v>
+        <v>0.5805457556077515</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2238628681118355</v>
+        <v>0.2254128681118354</v>
       </c>
       <c r="C100">
-        <v>-3.155227581218608</v>
+        <v>-3.278796252262449</v>
       </c>
       <c r="D100">
-        <v>4.188172418781392</v>
+        <v>4.162903747737551</v>
       </c>
       <c r="E100">
-        <v>9.1434</v>
+        <v>9.2417</v>
       </c>
       <c r="F100">
-        <v>9.6334</v>
+        <v>9.7317</v>
       </c>
       <c r="G100">
         <v>2.29</v>
@@ -9487,37 +9487,37 @@
         <v>1.123</v>
       </c>
       <c r="M100">
-        <v>1.93438672</v>
+        <v>1.95412536</v>
       </c>
       <c r="N100">
-        <v>-0.81138672</v>
+        <v>-0.8311253600000001</v>
       </c>
       <c r="O100">
-        <v>-0.20284668</v>
+        <v>-0.20778134</v>
       </c>
       <c r="P100">
-        <v>-0.6085400400000001</v>
+        <v>-0.6233440200000001</v>
       </c>
       <c r="Q100">
-        <v>-0.27154004</v>
+        <v>-0.2863440200000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.781969855235717</v>
+        <v>5.518139710471434</v>
       </c>
       <c r="T100">
-        <v>26.46085370657992</v>
+        <v>52.92170741315983</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1451364389019379</v>
+        <v>0.1436704142665647</v>
       </c>
       <c r="W100">
-        <v>0.1716566030684909</v>
+        <v>0.1719509808152738</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5805457556077515</v>
+        <v>0.574681657066259</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2254128681118354</v>
-      </c>
-      <c r="C101">
-        <v>-3.278796252262449</v>
-      </c>
-      <c r="D101">
-        <v>4.162903747737551</v>
-      </c>
-      <c r="E101">
-        <v>9.2417</v>
-      </c>
-      <c r="F101">
-        <v>9.7317</v>
-      </c>
-      <c r="G101">
-        <v>2.29</v>
-      </c>
-      <c r="H101">
-        <v>9.34</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.46</v>
-      </c>
-      <c r="K101">
-        <v>0.337</v>
-      </c>
-      <c r="L101">
-        <v>1.123</v>
-      </c>
-      <c r="M101">
-        <v>1.95412536</v>
-      </c>
-      <c r="N101">
-        <v>-0.8311253600000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.20778134</v>
-      </c>
-      <c r="P101">
-        <v>-0.6233440200000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.2863440200000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.518139710471434</v>
-      </c>
-      <c r="T101">
-        <v>52.92170741315983</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1436704142665647</v>
-      </c>
-      <c r="W101">
-        <v>0.1719509808152738</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.574681657066259</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
